--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="174">
   <si>
     <t>_Id</t>
   </si>
@@ -67,10 +67,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Layer</t>
-  </si>
-  <si>
-    <t>Memo</t>
+    <t>GroupId</t>
+  </si>
+  <si>
+    <t>BossId</t>
   </si>
   <si>
     <t>DropLevel</t>
@@ -97,7 +97,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>新手小村</t>
+    <t xml:space="preserve">暮色草场 </t>
   </si>
   <si>
     <t>10</t>
@@ -109,10 +109,7 @@
     <t>10,250,1000</t>
   </si>
   <si>
-    <t>新手村外</t>
-  </si>
-  <si>
-    <t>2阶技能</t>
+    <t>磷火墓地</t>
   </si>
   <si>
     <t>20</t>
@@ -124,7 +121,7 @@
     <t>10,250,538,1000</t>
   </si>
   <si>
-    <t>自然农场</t>
+    <t>碎骨荒原</t>
   </si>
   <si>
     <t>30</t>
@@ -133,10 +130,7 @@
     <t>200030,300010,300020,101</t>
   </si>
   <si>
-    <t>老兵之城</t>
-  </si>
-  <si>
-    <t>3阶技能</t>
+    <t>红月沙地</t>
   </si>
   <si>
     <t>40</t>
@@ -148,7 +142,7 @@
     <t>10,250,538,1160,1000</t>
   </si>
   <si>
-    <t>兽人森林</t>
+    <t>寒露石径</t>
   </si>
   <si>
     <t>50</t>
@@ -157,7 +151,7 @@
     <t>200050,300010,300020,300030,101</t>
   </si>
   <si>
-    <t>蝙蝠洞穴</t>
+    <t>落日石阵</t>
   </si>
   <si>
     <t>60</t>
@@ -166,10 +160,7 @@
     <t>200060,300010,300020,300030,101</t>
   </si>
   <si>
-    <t>骷髅洞</t>
-  </si>
-  <si>
-    <t>4阶技能</t>
+    <t>腐卵泥潭</t>
   </si>
   <si>
     <t>70</t>
@@ -181,7 +172,7 @@
     <t>10,250,538,1160,2500,1000</t>
   </si>
   <si>
-    <t>黑暗通道</t>
+    <t>黑石洞穴</t>
   </si>
   <si>
     <t>80</t>
@@ -190,7 +181,7 @@
     <t>200080,300010,300020,300030,300040,101</t>
   </si>
   <si>
-    <t>僵尸洞</t>
+    <t>瘴气河湾</t>
   </si>
   <si>
     <t>90</t>
@@ -199,7 +190,7 @@
     <t>200090,300010,300020,300030,300040,101</t>
   </si>
   <si>
-    <t>毒蛇谷</t>
+    <t>灼烧矿道</t>
   </si>
   <si>
     <t>100</t>
@@ -208,10 +199,7 @@
     <t>200100,300010,300020,300030,300040,101</t>
   </si>
   <si>
-    <t>野狼山</t>
-  </si>
-  <si>
-    <t>5阶技能</t>
+    <t>嗜血岩洞</t>
   </si>
   <si>
     <t>110</t>
@@ -223,7 +211,7 @@
     <t>10,250,538,1160,2500,5386,1000</t>
   </si>
   <si>
-    <t>沙虫洞</t>
+    <t>剧毒泥潭</t>
   </si>
   <si>
     <t>120</t>
@@ -232,7 +220,7 @@
     <t>200120,300010,300020,300030,300040,300050,101</t>
   </si>
   <si>
-    <t>鹰愁涧</t>
+    <t>焦炭回廊</t>
   </si>
   <si>
     <t>130</t>
@@ -241,7 +229,7 @@
     <t>200130,300010,300020,300030,300040,300050,101</t>
   </si>
   <si>
-    <t>角虫谷</t>
+    <t>庭院废墟</t>
   </si>
   <si>
     <t>140</t>
@@ -250,10 +238,7 @@
     <t>200140,300010,300020,300030,300040,300050,101</t>
   </si>
   <si>
-    <t>蜈蚣洞</t>
-  </si>
-  <si>
-    <t>6阶技能</t>
+    <t>霜晶矿脉</t>
   </si>
   <si>
     <t>150</t>
@@ -265,7 +250,7 @@
     <t>10,250,538,1160,2500,5386,11603,1000</t>
   </si>
   <si>
-    <t>钳虫洞</t>
+    <t>静电溶洞</t>
   </si>
   <si>
     <t>160</t>
@@ -274,7 +259,7 @@
     <t>200160,300010,300020,300030,300040,300050,300060,101</t>
   </si>
   <si>
-    <t>蠕虫洞</t>
+    <t>暗杀回廊</t>
   </si>
   <si>
     <t>170</t>
@@ -283,7 +268,7 @@
     <t>200170,300010,300020,300030,300040,300050,300060,101</t>
   </si>
   <si>
-    <t>魔猪大厅</t>
+    <t>巨型遗迹</t>
   </si>
   <si>
     <t>180</t>
@@ -292,7 +277,7 @@
     <t>200180,300010,300020,300030,300040,300050,300060,101</t>
   </si>
   <si>
-    <t>魔猪教堂</t>
+    <t>风化废墟</t>
   </si>
   <si>
     <t>190</t>
@@ -301,7 +286,7 @@
     <t>200190,300010,300020,300030,300040,300050,300060,101</t>
   </si>
   <si>
-    <t>世外桃源</t>
+    <t>寒霜古墓</t>
   </si>
   <si>
     <t>200</t>
@@ -310,10 +295,7 @@
     <t>200200,300010,300020,300030,300040,300050,300060,101</t>
   </si>
   <si>
-    <t>魔族禁地</t>
-  </si>
-  <si>
-    <t>7阶技能</t>
+    <t>雷鸣崖</t>
   </si>
   <si>
     <t>210</t>
@@ -325,7 +307,7 @@
     <t>10,500,500,500,1250,2500,5000,10000,1000</t>
   </si>
   <si>
-    <t>魔族神殿</t>
+    <t>恶咒神庙</t>
   </si>
   <si>
     <t>220</t>
@@ -334,7 +316,7 @@
     <t>200220,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>邪魔禁地</t>
+    <t>闪电峰顶</t>
   </si>
   <si>
     <t>230</t>
@@ -343,7 +325,7 @@
     <t>200230,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>邪魔神殿</t>
+    <t>古代殉葬坑</t>
   </si>
   <si>
     <t>240</t>
@@ -352,7 +334,7 @@
     <t>200240,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>封魔神殿</t>
+    <t>迷幻小径</t>
   </si>
   <si>
     <t>250</t>
@@ -361,7 +343,7 @@
     <t>200250,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>烈焰神殿</t>
+    <t>藤蔓密道</t>
   </si>
   <si>
     <t>260</t>
@@ -370,7 +352,7 @@
     <t>200260,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>封邪神殿</t>
+    <t>黑水潭</t>
   </si>
   <si>
     <t>270</t>
@@ -379,7 +361,7 @@
     <t>200270,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>尸魔神殿</t>
+    <t>角斗场废墟</t>
   </si>
   <si>
     <t>280</t>
@@ -388,7 +370,7 @@
     <t>200280,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>骨魔神殿</t>
+    <t>亡者塔楼</t>
   </si>
   <si>
     <t>290</t>
@@ -397,7 +379,7 @@
     <t>200290,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>魔牛神殿</t>
+    <t>翡翠梦境</t>
   </si>
   <si>
     <t>300</t>
@@ -406,7 +388,7 @@
     <t>200300,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>水龙谷</t>
+    <t>蜂巢巢穴</t>
   </si>
   <si>
     <t>310</t>
@@ -415,7 +397,7 @@
     <t>200310,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>土龙谷</t>
+    <t xml:space="preserve"> 暗杀猎场</t>
   </si>
   <si>
     <t>320</t>
@@ -424,7 +406,7 @@
     <t>200320,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>毒龙谷</t>
+    <t>冰霜隧道</t>
   </si>
   <si>
     <t>330</t>
@@ -433,7 +415,7 @@
     <t>200330,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>火龙谷</t>
+    <t>雷霆高地</t>
   </si>
   <si>
     <t>340</t>
@@ -442,7 +424,7 @@
     <t>200340,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>冰龙谷</t>
+    <t>烈火祭坛</t>
   </si>
   <si>
     <t>350</t>
@@ -451,10 +433,7 @@
     <t>200350,300010,300020,300030,300040,300050,300060,300070,101</t>
   </si>
   <si>
-    <t>幻影小村</t>
-  </si>
-  <si>
-    <t>8阶技能</t>
+    <t>地心熔炉</t>
   </si>
   <si>
     <t>360</t>
@@ -466,7 +445,7 @@
     <t>10,500,500,500,1250,2500,2500,5000,100000,1000</t>
   </si>
   <si>
-    <t>幻影村外</t>
+    <t>恶臭坑</t>
   </si>
   <si>
     <t>370</t>
@@ -475,7 +454,7 @@
     <t>200370,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
   </si>
   <si>
-    <t>幻影农场</t>
+    <t>迷幻花海</t>
   </si>
   <si>
     <t>380</t>
@@ -484,7 +463,7 @@
     <t>200380,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
   </si>
   <si>
-    <t>幻影老城</t>
+    <t>幼龙巢穴</t>
   </si>
   <si>
     <t>390</t>
@@ -493,7 +472,7 @@
     <t>200390,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
   </si>
   <si>
-    <t>幻影森林</t>
+    <t>午夜街道</t>
   </si>
   <si>
     <t>400</t>
@@ -502,10 +481,7 @@
     <t>200400,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
   </si>
   <si>
-    <t>幻影蝠洞</t>
-  </si>
-  <si>
-    <t>专属1-2</t>
+    <t>血斧营地</t>
   </si>
   <si>
     <t>410</t>
@@ -515,6 +491,96 @@
   </si>
   <si>
     <t>10,500,500,500,1250,2500,2500,5000,100000,1000,15000</t>
+  </si>
+  <si>
+    <t>雷暴尖塔</t>
+  </si>
+  <si>
+    <t>永冻墓道</t>
+  </si>
+  <si>
+    <t>爆裂地穴</t>
+  </si>
+  <si>
+    <t>毒瘴山谷</t>
+  </si>
+  <si>
+    <t>雷暴堡垒</t>
+  </si>
+  <si>
+    <t>暗黑祭坛</t>
+  </si>
+  <si>
+    <t>万年冰棺</t>
+  </si>
+  <si>
+    <t>极冰高原</t>
+  </si>
+  <si>
+    <t>鬼眼蛛巢</t>
+  </si>
+  <si>
+    <t>飓风祭坛</t>
+  </si>
+  <si>
+    <t>岩浆裂隙</t>
+  </si>
+  <si>
+    <t>邪教圣地</t>
+  </si>
+  <si>
+    <t>刺蔓花圃</t>
+  </si>
+  <si>
+    <t>无尽裂隙</t>
+  </si>
+  <si>
+    <t>猩红台地</t>
+  </si>
+  <si>
+    <t>寒冰湖岸</t>
+  </si>
+  <si>
+    <t>死亡骑营</t>
+  </si>
+  <si>
+    <t>黑洞奇点</t>
+  </si>
+  <si>
+    <t>剧毒湿地</t>
+  </si>
+  <si>
+    <t>火焰舞场</t>
+  </si>
+  <si>
+    <t>冰霜箭阵</t>
+  </si>
+  <si>
+    <t>魔像工坊</t>
+  </si>
+  <si>
+    <t>暗夜神殿</t>
+  </si>
+  <si>
+    <t>远古龙墓</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 熔岩核心</t>
+  </si>
+  <si>
+    <t>雷霆溶洞</t>
+  </si>
+  <si>
+    <t>深渊裂隙</t>
+  </si>
+  <si>
+    <t>血月祭坛</t>
+  </si>
+  <si>
+    <t>起源圣殿</t>
+  </si>
+  <si>
+    <t>失落神域</t>
   </si>
 </sst>
 </file>
@@ -1520,12 +1586,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J46"/>
+  <dimension ref="C3:J77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="4" max="7" width="11.6272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="60.0909090909091" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41.6363636363636" style="1" customWidth="1"/>
     <col min="9" max="9" width="70.5" style="1" customWidth="1"/>
     <col min="10" max="16381" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="16382" max="16384" width="9.25454545454545" style="1"/>
@@ -1590,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>9</v>
@@ -1633,17 +1699,15 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:10">
@@ -1651,19 +1715,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:10">
@@ -1671,22 +1735,20 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:10">
@@ -1694,19 +1756,22 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:10">
@@ -1714,19 +1779,22 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:10">
@@ -1734,22 +1802,20 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:10">
@@ -1757,19 +1823,19 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:10">
@@ -1777,19 +1843,19 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:10">
@@ -1797,19 +1863,19 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:10">
@@ -1817,22 +1883,22 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>2</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:9">
@@ -1840,19 +1906,22 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:9">
@@ -1860,19 +1929,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E18" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:9">
@@ -1880,19 +1949,19 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:9">
@@ -1900,22 +1969,20 @@
         <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:9">
@@ -1923,19 +1990,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E21" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:9">
@@ -1943,19 +2010,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E22" s="1">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
+        <v>3</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:9">
@@ -1963,19 +2033,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E23" s="1">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:9">
@@ -1983,19 +2056,19 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E24" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:9">
@@ -2003,19 +2076,19 @@
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E25" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:9">
@@ -2023,22 +2096,20 @@
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>84</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:9">
@@ -2046,19 +2117,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:9">
@@ -2066,19 +2137,22 @@
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E28" s="1">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F28" s="1">
+        <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:9">
@@ -2086,19 +2160,22 @@
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E29" s="1">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F29" s="1">
+        <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:9">
@@ -2106,19 +2183,19 @@
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E30" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:9">
@@ -2126,19 +2203,19 @@
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E31" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:9">
@@ -2146,19 +2223,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E32" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:9">
@@ -2166,19 +2243,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E33" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:9">
@@ -2186,19 +2263,22 @@
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E34" s="1">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F34" s="1">
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:9">
@@ -2206,19 +2286,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E35" s="1">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:9">
@@ -2226,19 +2309,19 @@
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E36" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:9">
@@ -2246,19 +2329,19 @@
         <v>32</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E37" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:9">
@@ -2266,19 +2349,19 @@
         <v>33</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E38" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:9">
@@ -2286,19 +2369,19 @@
         <v>34</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E39" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:9">
@@ -2306,19 +2389,22 @@
         <v>35</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E40" s="1">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="F40" s="1">
+        <v>6</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:9">
@@ -2326,22 +2412,22 @@
         <v>36</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E41" s="1">
-        <v>2</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>131</v>
+        <v>6</v>
+      </c>
+      <c r="F41" s="1">
+        <v>6</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:9">
@@ -2349,19 +2435,19 @@
         <v>37</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E42" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:9">
@@ -2369,19 +2455,19 @@
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E43" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:9">
@@ -2389,19 +2475,19 @@
         <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E44" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:9">
@@ -2409,19 +2495,19 @@
         <v>40</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E45" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:9">
@@ -2429,22 +2515,675 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" s="1">
+        <v>7</v>
+      </c>
+      <c r="F46" s="1">
+        <v>7</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:9">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E47" s="1">
+        <v>7</v>
+      </c>
+      <c r="F47" s="1">
+        <v>7</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:9">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="1">
+        <v>8</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:9">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="1">
+        <v>8</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:9">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E46" s="1">
-        <v>2</v>
-      </c>
-      <c r="F46" s="1" t="s">
+      <c r="E50" s="1">
+        <v>8</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:9">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="E51" s="1">
+        <v>8</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:9">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="E52" s="1">
+        <v>8</v>
+      </c>
+      <c r="F52" s="1">
+        <v>8</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:9">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="E53" s="1">
+        <v>8</v>
+      </c>
+      <c r="F53" s="1">
+        <v>8</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:9">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>151</v>
+      </c>
+      <c r="E54" s="1">
+        <v>9</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:9">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E55" s="1">
+        <v>9</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:9">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="1">
+        <v>9</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:9">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57" s="1">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:9">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="1">
+        <v>9</v>
+      </c>
+      <c r="F58" s="1">
+        <v>9</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:9">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E59" s="1">
+        <v>9</v>
+      </c>
+      <c r="F59" s="1">
+        <v>9</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:9">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" s="1">
+        <v>10</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:9">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E61" s="1">
+        <v>10</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:9">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E62" s="1">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:9">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" s="1">
+        <v>10</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:9">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E64" s="1">
+        <v>10</v>
+      </c>
+      <c r="F64" s="1">
+        <v>10</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:9">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" s="1">
+        <v>10</v>
+      </c>
+      <c r="F65" s="1">
+        <v>10</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:9">
+      <c r="C66" s="1">
+        <v>61</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E66" s="1">
+        <v>11</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:9">
+      <c r="C67" s="1">
+        <v>62</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E67" s="1">
+        <v>11</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:9">
+      <c r="C68" s="1">
+        <v>63</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E68" s="1">
+        <v>11</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:9">
+      <c r="C69" s="1">
+        <v>64</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E69" s="1">
+        <v>11</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:9">
+      <c r="C70" s="1">
+        <v>65</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E70" s="1">
+        <v>11</v>
+      </c>
+      <c r="F70" s="1">
+        <v>11</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:9">
+      <c r="C71" s="1">
+        <v>66</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E71" s="1">
+        <v>11</v>
+      </c>
+      <c r="F71" s="1">
+        <v>11</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:9">
+      <c r="C72" s="1">
+        <v>67</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="1">
+        <v>12</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:9">
+      <c r="C73" s="1">
+        <v>68</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="1">
+        <v>12</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:9">
+      <c r="C74" s="1">
+        <v>69</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" s="1">
+        <v>12</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:9">
+      <c r="C75" s="1">
+        <v>70</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="1">
+        <v>12</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:9">
+      <c r="C76" s="1">
+        <v>71</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E76" s="1">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1">
+        <v>12</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:9">
+      <c r="C77" s="1">
+        <v>72</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" s="1">
+        <v>12</v>
+      </c>
+      <c r="F77" s="1">
+        <v>12</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2452,7 +3191,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 C6:C46 C47:C1048576" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -50,7 +50,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-掉落ID：几率（万分比）</t>
+组合掉落</t>
         </r>
       </text>
     </comment>
@@ -59,7 +59,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_Id</t>
   </si>
@@ -73,15 +76,18 @@
     <t>BossId</t>
   </si>
   <si>
-    <t>DropLevel</t>
-  </si>
-  <si>
     <t>地图Id掉落</t>
   </si>
   <si>
     <t>DropRateList</t>
   </si>
   <si>
+    <t>BaseIdList</t>
+  </si>
+  <si>
+    <t>BaseRateList</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -97,490 +103,247 @@
     <t>int[]</t>
   </si>
   <si>
-    <t xml:space="preserve">暮色草场 </t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>200010,300010,101</t>
-  </si>
-  <si>
-    <t>10,250,1000</t>
+    <t>暮色草场</t>
+  </si>
+  <si>
+    <t>2001,4001,5001</t>
+  </si>
+  <si>
+    <t>30,3000,3000</t>
+  </si>
+  <si>
+    <t>30001</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
   <si>
     <t>磷火墓地</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>200020,300010,300020,101</t>
-  </si>
-  <si>
-    <t>10,250,538,1000</t>
+    <t>2002,4001,5001</t>
   </si>
   <si>
     <t>碎骨荒原</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>200030,300010,300020,101</t>
+    <t>2003,4001,5001</t>
   </si>
   <si>
     <t>红月沙地</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>200040,300010,300020,300030,101</t>
-  </si>
-  <si>
-    <t>10,250,538,1160,1000</t>
-  </si>
-  <si>
-    <t>寒露石径</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>200050,300010,300020,300030,101</t>
+    <t>2004,4002,5001</t>
+  </si>
+  <si>
+    <t>黑石洞穴</t>
+  </si>
+  <si>
+    <t>2005,4002,5001</t>
   </si>
   <si>
     <t>落日石阵</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>200060,300010,300020,300030,101</t>
+    <t>2006,4002,5001</t>
   </si>
   <si>
     <t>腐卵泥潭</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>200070,300010,300020,300030,300040,101</t>
-  </si>
-  <si>
-    <t>10,250,538,1160,2500,1000</t>
-  </si>
-  <si>
-    <t>黑石洞穴</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>200080,300010,300020,300030,300040,101</t>
+    <t>血色废墟</t>
+  </si>
+  <si>
+    <t>裂土石径</t>
+  </si>
+  <si>
+    <t>黑暗森林</t>
   </si>
   <si>
     <t>瘴气河湾</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>200090,300010,300020,300030,300040,101</t>
-  </si>
-  <si>
-    <t>灼烧矿道</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>200100,300010,300020,300030,300040,101</t>
-  </si>
-  <si>
-    <t>嗜血岩洞</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>200110,300010,300020,300030,300040,300050,101</t>
-  </si>
-  <si>
-    <t>10,250,538,1160,2500,5386,1000</t>
-  </si>
-  <si>
     <t>剧毒泥潭</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>200120,300010,300020,300030,300040,300050,101</t>
-  </si>
-  <si>
-    <t>焦炭回廊</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>200130,300010,300020,300030,300040,300050,101</t>
-  </si>
-  <si>
-    <t>庭院废墟</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>200140,300010,300020,300030,300040,300050,101</t>
-  </si>
-  <si>
-    <t>霜晶矿脉</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>200150,300010,300020,300030,300040,300050,300060,101</t>
-  </si>
-  <si>
-    <t>10,250,538,1160,2500,5386,11603,1000</t>
-  </si>
-  <si>
-    <t>静电溶洞</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>200160,300010,300020,300030,300040,300050,300060,101</t>
-  </si>
-  <si>
-    <t>暗杀回廊</t>
-  </si>
-  <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>200170,300010,300020,300030,300040,300050,300060,101</t>
-  </si>
-  <si>
-    <t>巨型遗迹</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>200180,300010,300020,300030,300040,300050,300060,101</t>
-  </si>
-  <si>
-    <t>风化废墟</t>
-  </si>
-  <si>
-    <t>190</t>
-  </si>
-  <si>
-    <t>200190,300010,300020,300030,300040,300050,300060,101</t>
-  </si>
-  <si>
-    <t>寒霜古墓</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>200200,300010,300020,300030,300040,300050,300060,101</t>
-  </si>
-  <si>
-    <t>雷鸣崖</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>200210,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>10,500,500,500,1250,2500,5000,10000,1000</t>
-  </si>
-  <si>
-    <t>恶咒神庙</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
-    <t>200220,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>闪电峰顶</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>200230,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>古代殉葬坑</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>200240,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>迷幻小径</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>200250,300010,300020,300030,300040,300050,300060,300070,101</t>
+    <t>废石小径</t>
+  </si>
+  <si>
+    <t>废弃矿道</t>
+  </si>
+  <si>
+    <t>绝望坑道</t>
+  </si>
+  <si>
+    <t>血煞溶洞</t>
+  </si>
+  <si>
+    <t>归宿祭坛</t>
+  </si>
+  <si>
+    <t>黄泉洞府</t>
+  </si>
+  <si>
+    <t>魅惑花园</t>
   </si>
   <si>
     <t>藤蔓密道</t>
   </si>
   <si>
-    <t>260</t>
-  </si>
-  <si>
-    <t>200260,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
     <t>黑水潭</t>
   </si>
   <si>
-    <t>270</t>
-  </si>
-  <si>
-    <t>200270,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>角斗场废墟</t>
-  </si>
-  <si>
-    <t>280</t>
-  </si>
-  <si>
-    <t>200280,300010,300020,300030,300040,300050,300060,300070,101</t>
+    <t>望月高台</t>
+  </si>
+  <si>
+    <t>毒瘴山谷</t>
+  </si>
+  <si>
+    <t>梦境之树</t>
+  </si>
+  <si>
+    <t>荒漠边缘</t>
+  </si>
+  <si>
+    <t>遗忘高地</t>
+  </si>
+  <si>
+    <t>遗弃坟场</t>
+  </si>
+  <si>
+    <t>幽暗灵墓</t>
   </si>
   <si>
     <t>亡者塔楼</t>
   </si>
   <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>200290,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>翡翠梦境</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>200300,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>蜂巢巢穴</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>200310,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 暗杀猎场</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>200320,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>冰霜隧道</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>200330,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>雷霆高地</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>200340,300010,300020,300030,300040,300050,300060,300070,101</t>
-  </si>
-  <si>
-    <t>烈火祭坛</t>
-  </si>
-  <si>
-    <t>350</t>
-  </si>
-  <si>
-    <t>200350,300010,300020,300030,300040,300050,300060,300070,101</t>
+    <t>埋骨之地</t>
+  </si>
+  <si>
+    <t>蛮鬃外围</t>
+  </si>
+  <si>
+    <t>荆棘围栏</t>
+  </si>
+  <si>
+    <t>碎石校场</t>
+  </si>
+  <si>
+    <t>图腾祭坛</t>
+  </si>
+  <si>
+    <t>觐见之路</t>
+  </si>
+  <si>
+    <t>钢鬃王座</t>
+  </si>
+  <si>
+    <t>地穴入口</t>
+  </si>
+  <si>
+    <t>幽火隧道</t>
+  </si>
+  <si>
+    <t>岩浆裂隙</t>
+  </si>
+  <si>
+    <t>烈焰围栏</t>
+  </si>
+  <si>
+    <t>焰姬大厅</t>
   </si>
   <si>
     <t>地心熔炉</t>
   </si>
   <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>200360,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
-  </si>
-  <si>
-    <t>10,500,500,500,1250,2500,2500,5000,100000,1000</t>
-  </si>
-  <si>
-    <t>恶臭坑</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>200370,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
-  </si>
-  <si>
-    <t>迷幻花海</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>200380,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
-  </si>
-  <si>
-    <t>幼龙巢穴</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>200390,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
-  </si>
-  <si>
-    <t>午夜街道</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>200400,300010,300020,300030,300040,300050,300060,300070,300080,102</t>
-  </si>
-  <si>
-    <t>血斧营地</t>
-  </si>
-  <si>
-    <t>410</t>
-  </si>
-  <si>
-    <t>200410,300010,300020,300030,300040,300050,300060,300070,300080,102,501</t>
-  </si>
-  <si>
-    <t>10,500,500,500,1250,2500,2500,5000,100000,1000,15000</t>
-  </si>
-  <si>
-    <t>雷暴尖塔</t>
-  </si>
-  <si>
     <t>永冻墓道</t>
   </si>
   <si>
-    <t>爆裂地穴</t>
-  </si>
-  <si>
-    <t>毒瘴山谷</t>
-  </si>
-  <si>
-    <t>雷暴堡垒</t>
-  </si>
-  <si>
-    <t>暗黑祭坛</t>
-  </si>
-  <si>
-    <t>万年冰棺</t>
-  </si>
-  <si>
-    <t>极冰高原</t>
+    <t>冰冷大厅</t>
+  </si>
+  <si>
+    <t>寒冰湖岸</t>
+  </si>
+  <si>
+    <t>冰霜平原</t>
+  </si>
+  <si>
+    <t>冰霜高地</t>
+  </si>
+  <si>
+    <t>凛冽王宫</t>
   </si>
   <si>
     <t>鬼眼蛛巢</t>
   </si>
   <si>
-    <t>飓风祭坛</t>
-  </si>
-  <si>
-    <t>岩浆裂隙</t>
-  </si>
-  <si>
-    <t>邪教圣地</t>
-  </si>
-  <si>
-    <t>刺蔓花圃</t>
+    <t>毒云沼泽</t>
+  </si>
+  <si>
+    <t>剧毒湿地</t>
+  </si>
+  <si>
+    <t>午夜迷宫</t>
+  </si>
+  <si>
+    <t>祭祀高台</t>
+  </si>
+  <si>
+    <t>诅咒祭坛</t>
+  </si>
+  <si>
+    <t>半人马营地</t>
+  </si>
+  <si>
+    <t>围猎场</t>
+  </si>
+  <si>
+    <t>萨满小屋</t>
+  </si>
+  <si>
+    <t>屠戮大厅</t>
+  </si>
+  <si>
+    <t>飞龙巢穴</t>
+  </si>
+  <si>
+    <t>王者角斗场</t>
   </si>
   <si>
     <t>无尽裂隙</t>
   </si>
   <si>
-    <t>猩红台地</t>
-  </si>
-  <si>
-    <t>寒冰湖岸</t>
-  </si>
-  <si>
-    <t>死亡骑营</t>
-  </si>
-  <si>
-    <t>黑洞奇点</t>
-  </si>
-  <si>
-    <t>剧毒湿地</t>
-  </si>
-  <si>
-    <t>火焰舞场</t>
-  </si>
-  <si>
-    <t>冰霜箭阵</t>
-  </si>
-  <si>
-    <t>魔像工坊</t>
-  </si>
-  <si>
-    <t>暗夜神殿</t>
-  </si>
-  <si>
-    <t>远古龙墓</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 熔岩核心</t>
-  </si>
-  <si>
-    <t>雷霆溶洞</t>
-  </si>
-  <si>
-    <t>深渊裂隙</t>
-  </si>
-  <si>
-    <t>血月祭坛</t>
-  </si>
-  <si>
-    <t>起源圣殿</t>
-  </si>
-  <si>
-    <t>失落神域</t>
+    <t>寂灭之地</t>
+  </si>
+  <si>
+    <t>猩红之界</t>
+  </si>
+  <si>
+    <t>起源之地</t>
+  </si>
+  <si>
+    <t>虚无战场</t>
+  </si>
+  <si>
+    <t>神王宝座</t>
+  </si>
+  <si>
+    <t>熔炉外围</t>
+  </si>
+  <si>
+    <t>地狱之门</t>
+  </si>
+  <si>
+    <t>女巫宫殿</t>
+  </si>
+  <si>
+    <t>地狱猎场</t>
+  </si>
+  <si>
+    <t>烈焰祭坛</t>
+  </si>
+  <si>
+    <t>毁灭王座</t>
   </si>
 </sst>
 </file>
@@ -593,7 +356,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +374,12 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0F1115"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1094,140 +863,157 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1586,177 +1372,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J77"/>
+  <dimension ref="C1:K77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="4" max="7" width="11.6272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="41.6363636363636" style="1" customWidth="1"/>
-    <col min="9" max="9" width="70.5" style="1" customWidth="1"/>
-    <col min="10" max="16381" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="16382" max="16384" width="9.25454545454545" style="1"/>
+    <col min="4" max="6" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="7" max="7" width="42.7272727272727" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.7272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7272727272727" style="1" customWidth="1"/>
+    <col min="12" max="16380" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="16381" max="16384" width="9.25454545454545" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:10">
+    <row r="1" customHeight="1" spans="3:11">
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:11">
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="3:11">
       <c r="C3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:11">
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" customHeight="1" spans="3:10">
-      <c r="C4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" customHeight="1" spans="3:10">
+    </row>
+    <row r="5" customHeight="1" spans="3:11">
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:10">
+        <v>13</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:11">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="G6" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:10">
+      <c r="H6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:11">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="J7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:10">
+    </row>
+    <row r="8" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="G8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:10">
+      <c r="H8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:10">
+      <c r="H9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1764,22 +1579,25 @@
       <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="G10" s="9" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:10">
+      <c r="H10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>30</v>
+      <c r="D11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1787,103 +1605,69 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:10">
+      <c r="G11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>33</v>
+      <c r="D12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+    </row>
+    <row r="13" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>37</v>
+      <c r="D13" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:10">
+    </row>
+    <row r="14" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>40</v>
+      <c r="D14" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:10">
+    </row>
+    <row r="15" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>43</v>
+      <c r="D15" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:10">
+    </row>
+    <row r="16" customHeight="1" spans="3:11">
       <c r="C16" s="1">
         <v>11</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>46</v>
+      <c r="D16" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -1891,22 +1675,13 @@
       <c r="F16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:9">
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>50</v>
+      <c r="D17" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -1914,103 +1689,57 @@
       <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:9">
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
       <c r="C18" s="1">
         <v>13</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>53</v>
+      <c r="D18" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:9">
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
       <c r="C19" s="1">
         <v>14</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>56</v>
+      <c r="D19" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:9">
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
       <c r="C20" s="1">
         <v>15</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>59</v>
+      <c r="D20" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:9">
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>63</v>
+      <c r="D21" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:9">
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
       <c r="C22" s="1">
         <v>17</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>66</v>
+      <c r="D22" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -2018,22 +1747,13 @@
       <c r="F22" s="1">
         <v>3</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:9">
+    </row>
+    <row r="23" customHeight="1" spans="3:6">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>69</v>
+      <c r="D23" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -2041,103 +1761,57 @@
       <c r="F23" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:9">
+    </row>
+    <row r="24" customHeight="1" spans="3:6">
       <c r="C24" s="1">
         <v>19</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>72</v>
+      <c r="D24" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:9">
+    </row>
+    <row r="25" customHeight="1" spans="3:6">
       <c r="C25" s="1">
         <v>20</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>75</v>
+      <c r="D25" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:9">
+    </row>
+    <row r="26" customHeight="1" spans="3:6">
       <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>78</v>
+      <c r="D26" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:9">
+    </row>
+    <row r="27" customHeight="1" spans="3:6">
       <c r="C27" s="1">
         <v>22</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>82</v>
+      <c r="D27" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:9">
+    </row>
+    <row r="28" customHeight="1" spans="3:6">
       <c r="C28" s="1">
         <v>23</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>85</v>
+      <c r="D28" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -2145,22 +1819,13 @@
       <c r="F28" s="1">
         <v>4</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:9">
+    </row>
+    <row r="29" customHeight="1" spans="3:6">
       <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>88</v>
+      <c r="D29" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -2168,102 +1833,57 @@
       <c r="F29" s="1">
         <v>4</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:9">
+    </row>
+    <row r="30" customHeight="1" spans="3:6">
       <c r="C30" s="1">
         <v>25</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>91</v>
+      <c r="D30" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:9">
+    </row>
+    <row r="31" customHeight="1" spans="3:6">
       <c r="C31" s="1">
         <v>26</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>94</v>
+      <c r="D31" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:9">
+    </row>
+    <row r="32" customHeight="1" spans="3:6">
       <c r="C32" s="1">
         <v>27</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>97</v>
+      <c r="D32" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:9">
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
       <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>100</v>
+      <c r="D33" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:9">
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
       <c r="C34" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>103</v>
+      <c r="D34" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
@@ -2271,22 +1891,13 @@
       <c r="F34" s="1">
         <v>5</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:9">
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>106</v>
+      <c r="D35" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -2294,102 +1905,57 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:9">
+    </row>
+    <row r="36" customHeight="1" spans="3:6">
       <c r="C36" s="1">
         <v>31</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>109</v>
+      <c r="D36" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:9">
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
       <c r="C37" s="1">
         <v>32</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>112</v>
+      <c r="D37" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:9">
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
       <c r="C38" s="1">
         <v>33</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>115</v>
+      <c r="D38" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:9">
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
       <c r="C39" s="1">
         <v>34</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>118</v>
+      <c r="D39" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:9">
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
       <c r="C40" s="1">
         <v>35</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>121</v>
+      <c r="D40" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
@@ -2397,22 +1963,13 @@
       <c r="F40" s="1">
         <v>6</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:9">
+    </row>
+    <row r="41" customHeight="1" spans="3:6">
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>124</v>
+      <c r="D41" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -2420,102 +1977,57 @@
       <c r="F41" s="1">
         <v>6</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:9">
+    </row>
+    <row r="42" customHeight="1" spans="3:6">
       <c r="C42" s="1">
         <v>37</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>128</v>
+      <c r="D42" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="E42" s="1">
         <v>7</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:9">
+    </row>
+    <row r="43" customHeight="1" spans="3:6">
       <c r="C43" s="1">
         <v>38</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>131</v>
+      <c r="D43" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="E43" s="1">
         <v>7</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:9">
+    </row>
+    <row r="44" customHeight="1" spans="3:6">
       <c r="C44" s="1">
         <v>39</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>134</v>
+      <c r="D44" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="E44" s="1">
         <v>7</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:9">
+    </row>
+    <row r="45" customHeight="1" spans="3:6">
       <c r="C45" s="1">
         <v>40</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>137</v>
+      <c r="D45" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:9">
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C46" s="1">
         <v>41</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>140</v>
+      <c r="D46" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="E46" s="1">
         <v>7</v>
@@ -2523,22 +2035,13 @@
       <c r="F46" s="1">
         <v>7</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:9">
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
       <c r="C47" s="1">
         <v>42</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>144</v>
+      <c r="D47" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="E47" s="1">
         <v>7</v>
@@ -2546,102 +2049,57 @@
       <c r="F47" s="1">
         <v>7</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:9">
+    </row>
+    <row r="48" customHeight="1" spans="3:6">
       <c r="C48" s="1">
         <v>43</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>145</v>
+      <c r="D48" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="E48" s="1">
         <v>8</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:9">
+    </row>
+    <row r="49" customHeight="1" spans="3:6">
       <c r="C49" s="1">
         <v>44</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>146</v>
+      <c r="D49" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="E49" s="1">
         <v>8</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:9">
+    </row>
+    <row r="50" customHeight="1" spans="3:6">
       <c r="C50" s="1">
         <v>45</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>147</v>
+      <c r="D50" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:9">
+    </row>
+    <row r="51" customHeight="1" spans="3:6">
       <c r="C51" s="1">
         <v>46</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>148</v>
+      <c r="D51" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="E51" s="1">
         <v>8</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:9">
+    </row>
+    <row r="52" customHeight="1" spans="3:6">
       <c r="C52" s="1">
         <v>47</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>149</v>
+      <c r="D52" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E52" s="1">
         <v>8</v>
@@ -2649,22 +2107,13 @@
       <c r="F52" s="1">
         <v>8</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:9">
+    </row>
+    <row r="53" customHeight="1" spans="3:6">
       <c r="C53" s="1">
         <v>48</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>150</v>
+      <c r="D53" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="E53" s="1">
         <v>8</v>
@@ -2672,102 +2121,57 @@
       <c r="F53" s="1">
         <v>8</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:9">
+    </row>
+    <row r="54" customHeight="1" spans="3:6">
       <c r="C54" s="1">
         <v>49</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>151</v>
+      <c r="D54" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E54" s="1">
         <v>9</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:9">
+    </row>
+    <row r="55" customHeight="1" spans="3:6">
       <c r="C55" s="1">
         <v>50</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>152</v>
+      <c r="D55" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="E55" s="1">
         <v>9</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:9">
+    </row>
+    <row r="56" customHeight="1" spans="3:6">
       <c r="C56" s="1">
         <v>51</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>153</v>
+      <c r="D56" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E56" s="1">
         <v>9</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:9">
+    </row>
+    <row r="57" customHeight="1" spans="3:6">
       <c r="C57" s="1">
         <v>52</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>154</v>
+      <c r="D57" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E57" s="1">
         <v>9</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:9">
+    </row>
+    <row r="58" customHeight="1" spans="3:6">
       <c r="C58" s="1">
         <v>53</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>16</v>
+      <c r="D58" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="E58" s="1">
         <v>9</v>
@@ -2775,22 +2179,13 @@
       <c r="F58" s="1">
         <v>9</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:9">
+    </row>
+    <row r="59" customHeight="1" spans="3:6">
       <c r="C59" s="1">
         <v>54</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>155</v>
+      <c r="D59" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="E59" s="1">
         <v>9</v>
@@ -2798,102 +2193,57 @@
       <c r="F59" s="1">
         <v>9</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:9">
+    </row>
+    <row r="60" customHeight="1" spans="3:6">
       <c r="C60" s="1">
         <v>55</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>156</v>
+      <c r="D60" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:9">
+    </row>
+    <row r="61" customHeight="1" spans="3:6">
       <c r="C61" s="1">
         <v>56</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>157</v>
+      <c r="D61" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="E61" s="1">
         <v>10</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:9">
+    </row>
+    <row r="62" customHeight="1" spans="3:6">
       <c r="C62" s="1">
         <v>57</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>158</v>
+      <c r="D62" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:9">
+    </row>
+    <row r="63" customHeight="1" spans="3:6">
       <c r="C63" s="1">
         <v>58</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>159</v>
+      <c r="D63" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="E63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:9">
+    </row>
+    <row r="64" customHeight="1" spans="3:6">
       <c r="C64" s="1">
         <v>59</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>160</v>
+      <c r="D64" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="E64" s="1">
         <v>10</v>
@@ -2901,22 +2251,13 @@
       <c r="F64" s="1">
         <v>10</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:9">
+    </row>
+    <row r="65" customHeight="1" spans="3:6">
       <c r="C65" s="1">
         <v>60</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>161</v>
+      <c r="D65" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="E65" s="1">
         <v>10</v>
@@ -2924,102 +2265,57 @@
       <c r="F65" s="1">
         <v>10</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:9">
+    </row>
+    <row r="66" customHeight="1" spans="3:6">
       <c r="C66" s="1">
         <v>61</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>162</v>
+      <c r="D66" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="E66" s="1">
         <v>11</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:9">
+    </row>
+    <row r="67" customHeight="1" spans="3:6">
       <c r="C67" s="1">
         <v>62</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>163</v>
+      <c r="D67" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="E67" s="1">
         <v>11</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:9">
+    </row>
+    <row r="68" customHeight="1" spans="3:6">
       <c r="C68" s="1">
         <v>63</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>164</v>
+      <c r="D68" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E68" s="1">
         <v>11</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:9">
+    </row>
+    <row r="69" customHeight="1" spans="3:6">
       <c r="C69" s="1">
         <v>64</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>165</v>
+      <c r="D69" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:9">
+    </row>
+    <row r="70" customHeight="1" spans="3:6">
       <c r="C70" s="1">
         <v>65</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>166</v>
+      <c r="D70" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="E70" s="1">
         <v>11</v>
@@ -3027,22 +2323,13 @@
       <c r="F70" s="1">
         <v>11</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:9">
+    </row>
+    <row r="71" customHeight="1" spans="3:6">
       <c r="C71" s="1">
         <v>66</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>167</v>
+      <c r="D71" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -3050,102 +2337,57 @@
       <c r="F71" s="1">
         <v>11</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:9">
+    </row>
+    <row r="72" customHeight="1" spans="3:6">
       <c r="C72" s="1">
         <v>67</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>168</v>
+      <c r="D72" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="E72" s="1">
         <v>12</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:9">
+    </row>
+    <row r="73" customHeight="1" spans="3:6">
       <c r="C73" s="1">
         <v>68</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>169</v>
+      <c r="D73" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="E73" s="1">
         <v>12</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:9">
+    </row>
+    <row r="74" customHeight="1" spans="3:6">
       <c r="C74" s="1">
         <v>69</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>170</v>
+      <c r="D74" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E74" s="1">
         <v>12</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:9">
+    </row>
+    <row r="75" customHeight="1" spans="3:6">
       <c r="C75" s="1">
         <v>70</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>171</v>
+      <c r="D75" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="E75" s="1">
         <v>12</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:9">
+    </row>
+    <row r="76" customHeight="1" spans="3:6">
       <c r="C76" s="1">
         <v>71</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>172</v>
+      <c r="D76" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="E76" s="1">
         <v>12</v>
@@ -3153,37 +2395,19 @@
       <c r="F76" s="1">
         <v>12</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:9">
+    </row>
+    <row r="77" customHeight="1" spans="3:6">
       <c r="C77" s="1">
         <v>72</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>173</v>
+      <c r="D77" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="E77" s="1">
         <v>12</v>
       </c>
       <c r="F77" s="1">
         <v>12</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="主线副本" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="95">
   <si>
     <t>#</t>
   </si>
@@ -1372,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:K77"/>
+  <dimension ref="C1:L77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -1386,17 +1386,23 @@
     <col min="16381" max="16384" width="9.25454545454545" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:11">
+    <row r="1" customHeight="1" spans="3:12">
       <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:11">
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:12">
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" customHeight="1" spans="3:11">
+      <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="3:11">
+    <row r="4" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1448,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="3:11">
+    <row r="5" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1474,7 +1480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:11">
+    <row r="6" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1497,7 +1503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:11">
+    <row r="7" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:11">
+    <row r="8" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:11">
+    <row r="9" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1566,7 +1572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:11">
+    <row r="10" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:11">
+    <row r="11" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1618,7 +1624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:11">
+    <row r="12" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1629,7 +1635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:11">
+    <row r="13" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1640,7 +1646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:11">
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1651,7 +1657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:11">
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1662,7 +1668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:11">
+    <row r="16" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
   <si>
     <t>#</t>
   </si>
@@ -112,10 +112,10 @@
     <t>30,3000,3000</t>
   </si>
   <si>
-    <t>30001</t>
-  </si>
-  <si>
-    <t>10000</t>
+    <t>30001,180001</t>
+  </si>
+  <si>
+    <t>10000,10000</t>
   </si>
   <si>
     <t>磷火墓地</t>
@@ -124,28 +124,43 @@
     <t>2002,4001,5001</t>
   </si>
   <si>
+    <t>30001,180002</t>
+  </si>
+  <si>
     <t>碎骨荒原</t>
   </si>
   <si>
     <t>2003,4001,5001</t>
   </si>
   <si>
+    <t>30001,180003</t>
+  </si>
+  <si>
     <t>红月沙地</t>
   </si>
   <si>
     <t>2004,4002,5001</t>
   </si>
   <si>
+    <t>30001,180004</t>
+  </si>
+  <si>
     <t>黑石洞穴</t>
   </si>
   <si>
     <t>2005,4002,5001</t>
   </si>
   <si>
+    <t>30001,180005</t>
+  </si>
+  <si>
     <t>落日石阵</t>
   </si>
   <si>
     <t>2006,4002,5001</t>
+  </si>
+  <si>
+    <t>30001,180006</t>
   </si>
   <si>
     <t>腐卵泥潭</t>
@@ -1520,7 +1535,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>18</v>
@@ -1531,19 +1546,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>18</v>
@@ -1554,19 +1569,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>18</v>
@@ -1577,7 +1592,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1586,13 +1601,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>18</v>
@@ -1603,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1612,13 +1627,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>18</v>
@@ -1629,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1640,7 +1655,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -1651,7 +1666,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -1662,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -1673,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -1687,7 +1702,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -1701,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -1712,7 +1727,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -1723,7 +1738,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -1734,7 +1749,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -1745,7 +1760,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -1759,7 +1774,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -1773,7 +1788,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
@@ -1784,7 +1799,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
@@ -1795,7 +1810,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
@@ -1806,7 +1821,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
@@ -1817,7 +1832,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -1831,7 +1846,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -1845,7 +1860,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
@@ -1856,7 +1871,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
@@ -1867,7 +1882,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
@@ -1878,7 +1893,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
@@ -1889,7 +1904,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
@@ -1903,7 +1918,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -1917,7 +1932,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
@@ -1928,7 +1943,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
@@ -1939,7 +1954,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
@@ -1950,7 +1965,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
@@ -1961,7 +1976,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
@@ -1975,7 +1990,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -1989,7 +2004,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E42" s="1">
         <v>7</v>
@@ -2000,7 +2015,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E43" s="1">
         <v>7</v>
@@ -2011,7 +2026,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E44" s="1">
         <v>7</v>
@@ -2022,7 +2037,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
@@ -2033,7 +2048,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E46" s="1">
         <v>7</v>
@@ -2047,7 +2062,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E47" s="1">
         <v>7</v>
@@ -2061,7 +2076,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E48" s="1">
         <v>8</v>
@@ -2072,7 +2087,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E49" s="1">
         <v>8</v>
@@ -2083,7 +2098,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
@@ -2094,7 +2109,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E51" s="1">
         <v>8</v>
@@ -2105,7 +2120,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E52" s="1">
         <v>8</v>
@@ -2119,7 +2134,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E53" s="1">
         <v>8</v>
@@ -2133,7 +2148,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E54" s="1">
         <v>9</v>
@@ -2144,7 +2159,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E55" s="1">
         <v>9</v>
@@ -2155,7 +2170,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E56" s="1">
         <v>9</v>
@@ -2166,7 +2181,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E57" s="1">
         <v>9</v>
@@ -2177,7 +2192,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E58" s="1">
         <v>9</v>
@@ -2191,7 +2206,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E59" s="1">
         <v>9</v>
@@ -2205,7 +2220,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
@@ -2216,7 +2231,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E61" s="1">
         <v>10</v>
@@ -2227,7 +2242,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
@@ -2238,7 +2253,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E63" s="1">
         <v>10</v>
@@ -2249,7 +2264,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E64" s="1">
         <v>10</v>
@@ -2263,7 +2278,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E65" s="1">
         <v>10</v>
@@ -2277,7 +2292,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E66" s="1">
         <v>11</v>
@@ -2288,7 +2303,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E67" s="1">
         <v>11</v>
@@ -2299,7 +2314,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E68" s="1">
         <v>11</v>
@@ -2310,7 +2325,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -2321,7 +2336,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E70" s="1">
         <v>11</v>
@@ -2335,7 +2350,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -2349,7 +2364,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E72" s="1">
         <v>12</v>
@@ -2360,7 +2375,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E73" s="1">
         <v>12</v>
@@ -2371,7 +2386,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E74" s="1">
         <v>12</v>
@@ -2382,7 +2397,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E75" s="1">
         <v>12</v>
@@ -2393,7 +2408,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E76" s="1">
         <v>12</v>
@@ -2407,7 +2422,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E77" s="1">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
   <si>
     <t>#</t>
   </si>
@@ -166,19 +166,55 @@
     <t>腐卵泥潭</t>
   </si>
   <si>
+    <t>2007,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180007</t>
+  </si>
+  <si>
     <t>血色废墟</t>
   </si>
   <si>
+    <t>2008,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180008</t>
+  </si>
+  <si>
     <t>裂土石径</t>
   </si>
   <si>
+    <t>2009,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180009</t>
+  </si>
+  <si>
     <t>黑暗森林</t>
   </si>
   <si>
+    <t>2010,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180010</t>
+  </si>
+  <si>
     <t>瘴气河湾</t>
   </si>
   <si>
+    <t>2011,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180011</t>
+  </si>
+  <si>
     <t>剧毒泥潭</t>
+  </si>
+  <si>
+    <t>2012,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180012</t>
   </si>
   <si>
     <t>废石小径</t>
@@ -1649,16 +1685,40 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
+      <c r="G12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -1666,10 +1726,22 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -1677,10 +1749,22 @@
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -1688,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -1696,13 +1780,25 @@
       <c r="F16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:6">
+      <c r="G16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:10">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -1710,57 +1806,69 @@
       <c r="F17" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:6">
+      <c r="G17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:10">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:6">
+    <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:6">
+    <row r="20" customHeight="1" spans="3:10">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:6">
+    <row r="21" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:6">
+    <row r="22" customHeight="1" spans="3:10">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -1769,12 +1877,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:6">
+    <row r="23" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -1783,56 +1891,56 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:6">
+    <row r="24" customHeight="1" spans="3:10">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:6">
+    <row r="25" customHeight="1" spans="3:10">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:6">
+    <row r="26" customHeight="1" spans="3:10">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:6">
+    <row r="27" customHeight="1" spans="3:10">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:6">
+    <row r="28" customHeight="1" spans="3:10">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -1841,12 +1949,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:6">
+    <row r="29" customHeight="1" spans="3:10">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -1855,34 +1963,34 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:6">
+    <row r="30" customHeight="1" spans="3:10">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:6">
+    <row r="31" customHeight="1" spans="3:10">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:6">
+    <row r="32" customHeight="1" spans="3:10">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
@@ -1893,7 +2001,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
@@ -1904,7 +2012,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
@@ -1918,7 +2026,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -1932,7 +2040,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
@@ -1943,7 +2051,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
@@ -1954,7 +2062,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
@@ -1965,7 +2073,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
@@ -1976,7 +2084,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
@@ -1990,7 +2098,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -2004,7 +2112,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E42" s="1">
         <v>7</v>
@@ -2015,7 +2123,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E43" s="1">
         <v>7</v>
@@ -2026,7 +2134,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E44" s="1">
         <v>7</v>
@@ -2037,7 +2145,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
@@ -2048,7 +2156,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E46" s="1">
         <v>7</v>
@@ -2062,7 +2170,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E47" s="1">
         <v>7</v>
@@ -2076,7 +2184,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E48" s="1">
         <v>8</v>
@@ -2087,7 +2195,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E49" s="1">
         <v>8</v>
@@ -2098,7 +2206,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
@@ -2109,7 +2217,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E51" s="1">
         <v>8</v>
@@ -2120,7 +2228,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E52" s="1">
         <v>8</v>
@@ -2134,7 +2242,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E53" s="1">
         <v>8</v>
@@ -2148,7 +2256,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="E54" s="1">
         <v>9</v>
@@ -2159,7 +2267,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E55" s="1">
         <v>9</v>
@@ -2170,7 +2278,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E56" s="1">
         <v>9</v>
@@ -2181,7 +2289,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E57" s="1">
         <v>9</v>
@@ -2192,7 +2300,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E58" s="1">
         <v>9</v>
@@ -2206,7 +2314,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E59" s="1">
         <v>9</v>
@@ -2220,7 +2328,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
@@ -2231,7 +2339,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E61" s="1">
         <v>10</v>
@@ -2242,7 +2350,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
@@ -2253,7 +2361,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="E63" s="1">
         <v>10</v>
@@ -2264,7 +2372,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E64" s="1">
         <v>10</v>
@@ -2278,7 +2386,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E65" s="1">
         <v>10</v>
@@ -2292,7 +2400,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E66" s="1">
         <v>11</v>
@@ -2303,7 +2411,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E67" s="1">
         <v>11</v>
@@ -2314,7 +2422,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E68" s="1">
         <v>11</v>
@@ -2325,7 +2433,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -2336,7 +2444,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E70" s="1">
         <v>11</v>
@@ -2350,7 +2458,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -2364,7 +2472,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E72" s="1">
         <v>12</v>
@@ -2375,7 +2483,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="E73" s="1">
         <v>12</v>
@@ -2386,7 +2494,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E74" s="1">
         <v>12</v>
@@ -2397,7 +2505,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E75" s="1">
         <v>12</v>
@@ -2408,7 +2516,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E76" s="1">
         <v>12</v>
@@ -2422,7 +2530,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E77" s="1">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -109,13 +109,13 @@
     <t>2001,4001,5001</t>
   </si>
   <si>
-    <t>30,3000,3000</t>
+    <t>30,6000,6000</t>
   </si>
   <si>
     <t>30001,180001</t>
   </si>
   <si>
-    <t>10000,10000</t>
+    <t>4000,8000</t>
   </si>
   <si>
     <t>磷火墓地</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="160">
   <si>
     <t>#</t>
   </si>
@@ -220,73 +220,217 @@
     <t>废石小径</t>
   </si>
   <si>
+    <t>2013,4005,5003</t>
+  </si>
+  <si>
+    <t>30001,180013</t>
+  </si>
+  <si>
     <t>废弃矿道</t>
   </si>
   <si>
+    <t>2014,4005,5003</t>
+  </si>
+  <si>
+    <t>30001,180014</t>
+  </si>
+  <si>
     <t>绝望坑道</t>
   </si>
   <si>
+    <t>2015,4005,5003</t>
+  </si>
+  <si>
+    <t>30001,180015</t>
+  </si>
+  <si>
     <t>血煞溶洞</t>
   </si>
   <si>
+    <t>2016,4006,5003</t>
+  </si>
+  <si>
+    <t>30001,180016</t>
+  </si>
+  <si>
     <t>归宿祭坛</t>
   </si>
   <si>
+    <t>2017,4006,5003</t>
+  </si>
+  <si>
+    <t>30001,180017</t>
+  </si>
+  <si>
     <t>黄泉洞府</t>
   </si>
   <si>
+    <t>2018,4006,5003</t>
+  </si>
+  <si>
+    <t>30001,180018</t>
+  </si>
+  <si>
     <t>魅惑花园</t>
   </si>
   <si>
+    <t>2019,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180019</t>
+  </si>
+  <si>
     <t>藤蔓密道</t>
   </si>
   <si>
+    <t>2020,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180020</t>
+  </si>
+  <si>
     <t>黑水潭</t>
   </si>
   <si>
+    <t>2021,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180021</t>
+  </si>
+  <si>
     <t>望月高台</t>
   </si>
   <si>
+    <t>2022,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180022</t>
+  </si>
+  <si>
     <t>毒瘴山谷</t>
   </si>
   <si>
+    <t>2023,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180023</t>
+  </si>
+  <si>
     <t>梦境之树</t>
   </si>
   <si>
+    <t>2024,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180024</t>
+  </si>
+  <si>
     <t>荒漠边缘</t>
   </si>
   <si>
+    <t>2025,4007,5005</t>
+  </si>
+  <si>
+    <t>30001,180025</t>
+  </si>
+  <si>
     <t>遗忘高地</t>
   </si>
   <si>
+    <t>2026,4007,5005</t>
+  </si>
+  <si>
+    <t>30001,180026</t>
+  </si>
+  <si>
     <t>遗弃坟场</t>
   </si>
   <si>
+    <t>2027,4007,5005</t>
+  </si>
+  <si>
+    <t>30001,180027</t>
+  </si>
+  <si>
     <t>幽暗灵墓</t>
   </si>
   <si>
+    <t>2028,4007,5005</t>
+  </si>
+  <si>
+    <t>30001,180028</t>
+  </si>
+  <si>
     <t>亡者塔楼</t>
   </si>
   <si>
+    <t>2029,4007,5005</t>
+  </si>
+  <si>
+    <t>30001,180029</t>
+  </si>
+  <si>
     <t>埋骨之地</t>
   </si>
   <si>
+    <t>2030,4007,5005</t>
+  </si>
+  <si>
+    <t>30001,180030</t>
+  </si>
+  <si>
     <t>蛮鬃外围</t>
   </si>
   <si>
+    <t>2031,4007,5006</t>
+  </si>
+  <si>
+    <t>30001,180031</t>
+  </si>
+  <si>
     <t>荆棘围栏</t>
   </si>
   <si>
+    <t>2032,4007,5006</t>
+  </si>
+  <si>
+    <t>30001,180032</t>
+  </si>
+  <si>
     <t>碎石校场</t>
   </si>
   <si>
+    <t>2033,4007,5006</t>
+  </si>
+  <si>
+    <t>30001,180033</t>
+  </si>
+  <si>
     <t>图腾祭坛</t>
   </si>
   <si>
+    <t>2034,4007,5006</t>
+  </si>
+  <si>
+    <t>30001,180034</t>
+  </si>
+  <si>
     <t>觐见之路</t>
   </si>
   <si>
+    <t>2035,4007,5006</t>
+  </si>
+  <si>
+    <t>30001,180035</t>
+  </si>
+  <si>
     <t>钢鬃王座</t>
+  </si>
+  <si>
+    <t>2036,4007,5006</t>
+  </si>
+  <si>
+    <t>30001,180036</t>
   </si>
   <si>
     <t>地穴入口</t>
@@ -579,12 +723,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1829,16 +1973,40 @@
       <c r="E18" s="1">
         <v>3</v>
       </c>
+      <c r="G18" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="19" customHeight="1" spans="3:10">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:10">
@@ -1846,21 +2014,45 @@
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
+      <c r="G20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" customHeight="1" spans="3:10">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:10">
@@ -1868,7 +2060,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -1876,19 +2068,43 @@
       <c r="F22" s="1">
         <v>3</v>
       </c>
+      <c r="G22" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="23" customHeight="1" spans="3:10">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
       </c>
       <c r="F23" s="1">
         <v>3</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:10">
@@ -1896,10 +2112,22 @@
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:10">
@@ -1907,10 +2135,22 @@
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:10">
@@ -1918,10 +2158,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:10">
@@ -1929,10 +2181,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:10">
@@ -1940,13 +2204,25 @@
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
       </c>
       <c r="F28" s="1">
         <v>4</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:10">
@@ -1954,13 +2230,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
       </c>
       <c r="F29" s="1">
         <v>4</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:10">
@@ -1968,10 +2256,22 @@
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:10">
@@ -1979,10 +2279,22 @@
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:10">
@@ -1990,29 +2302,53 @@
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:6">
+      <c r="G32" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:6">
+      <c r="G33" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
@@ -2020,13 +2356,25 @@
       <c r="F34" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:6">
+      <c r="G34" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -2034,57 +2382,117 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:6">
+      <c r="G35" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:6">
+      <c r="G36" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:6">
+      <c r="G37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:10">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:6">
+      <c r="G38" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:10">
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:6">
+      <c r="G39" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:10">
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
@@ -2092,13 +2500,25 @@
       <c r="F40" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:6">
+      <c r="G40" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:10">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -2106,57 +2526,69 @@
       <c r="F41" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:6">
+      <c r="G41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:10">
       <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="E42" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:6">
+    <row r="43" customHeight="1" spans="3:10">
       <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="E43" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:6">
+    <row r="44" customHeight="1" spans="3:10">
       <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:6">
+    <row r="45" customHeight="1" spans="3:10">
       <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
       <c r="C46" s="1">
         <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="E46" s="1">
         <v>7</v>
@@ -2165,12 +2597,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:6">
+    <row r="47" customHeight="1" spans="3:10">
       <c r="C47" s="1">
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="E47" s="1">
         <v>7</v>
@@ -2179,12 +2611,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:6">
+    <row r="48" customHeight="1" spans="3:10">
       <c r="C48" s="1">
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="E48" s="1">
         <v>8</v>
@@ -2195,7 +2627,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="E49" s="1">
         <v>8</v>
@@ -2206,7 +2638,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
@@ -2217,7 +2649,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
       <c r="E51" s="1">
         <v>8</v>
@@ -2228,7 +2660,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="E52" s="1">
         <v>8</v>
@@ -2242,7 +2674,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="E53" s="1">
         <v>8</v>
@@ -2256,7 +2688,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="E54" s="1">
         <v>9</v>
@@ -2267,7 +2699,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="E55" s="1">
         <v>9</v>
@@ -2278,7 +2710,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="E56" s="1">
         <v>9</v>
@@ -2289,7 +2721,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="E57" s="1">
         <v>9</v>
@@ -2300,7 +2732,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="E58" s="1">
         <v>9</v>
@@ -2314,7 +2746,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="E59" s="1">
         <v>9</v>
@@ -2328,7 +2760,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
@@ -2339,7 +2771,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="E61" s="1">
         <v>10</v>
@@ -2350,7 +2782,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
@@ -2361,7 +2793,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="E63" s="1">
         <v>10</v>
@@ -2372,7 +2804,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="E64" s="1">
         <v>10</v>
@@ -2386,7 +2818,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="E65" s="1">
         <v>10</v>
@@ -2400,7 +2832,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="E66" s="1">
         <v>11</v>
@@ -2411,7 +2843,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="E67" s="1">
         <v>11</v>
@@ -2422,7 +2854,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="E68" s="1">
         <v>11</v>
@@ -2433,7 +2865,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -2444,7 +2876,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="E70" s="1">
         <v>11</v>
@@ -2458,7 +2890,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -2472,7 +2904,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="E72" s="1">
         <v>12</v>
@@ -2483,7 +2915,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1">
         <v>12</v>
@@ -2494,7 +2926,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="E74" s="1">
         <v>12</v>
@@ -2505,7 +2937,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1">
         <v>12</v>
@@ -2516,7 +2948,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="E76" s="1">
         <v>12</v>
@@ -2530,7 +2962,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="E77" s="1">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="174">
   <si>
     <t>#</t>
   </si>
@@ -109,7 +109,7 @@
     <t>2001,4001,5001</t>
   </si>
   <si>
-    <t>30,6000,6000</t>
+    <t>15,6000,6000</t>
   </si>
   <si>
     <t>30001,180001</t>
@@ -124,6 +124,9 @@
     <t>2002,4001,5001</t>
   </si>
   <si>
+    <t>16,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180002</t>
   </si>
   <si>
@@ -133,6 +136,9 @@
     <t>2003,4001,5001</t>
   </si>
   <si>
+    <t>17,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180003</t>
   </si>
   <si>
@@ -142,6 +148,9 @@
     <t>2004,4002,5001</t>
   </si>
   <si>
+    <t>18,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180004</t>
   </si>
   <si>
@@ -151,6 +160,9 @@
     <t>2005,4002,5001</t>
   </si>
   <si>
+    <t>19,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180005</t>
   </si>
   <si>
@@ -169,6 +181,9 @@
     <t>2007,4003,5002</t>
   </si>
   <si>
+    <t>20,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180007</t>
   </si>
   <si>
@@ -196,6 +211,9 @@
     <t>2010,4004,5002</t>
   </si>
   <si>
+    <t>21,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180010</t>
   </si>
   <si>
@@ -223,6 +241,9 @@
     <t>2013,4005,5003</t>
   </si>
   <si>
+    <t>22,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180013</t>
   </si>
   <si>
@@ -250,6 +271,9 @@
     <t>2016,4006,5003</t>
   </si>
   <si>
+    <t>23,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180016</t>
   </si>
   <si>
@@ -277,6 +301,9 @@
     <t>2019,4007,5004</t>
   </si>
   <si>
+    <t>24,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180019</t>
   </si>
   <si>
@@ -304,6 +331,9 @@
     <t>2022,4007,5004</t>
   </si>
   <si>
+    <t>25,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180022</t>
   </si>
   <si>
@@ -331,6 +361,9 @@
     <t>2025,4007,5005</t>
   </si>
   <si>
+    <t>26,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180025</t>
   </si>
   <si>
@@ -358,6 +391,9 @@
     <t>2028,4007,5005</t>
   </si>
   <si>
+    <t>27,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180028</t>
   </si>
   <si>
@@ -385,6 +421,9 @@
     <t>2031,4007,5006</t>
   </si>
   <si>
+    <t>28,6000,6000</t>
+  </si>
+  <si>
     <t>30001,180031</t>
   </si>
   <si>
@@ -410,6 +449,9 @@
   </si>
   <si>
     <t>2034,4007,5006</t>
+  </si>
+  <si>
+    <t>29,6000,6000</t>
   </si>
   <si>
     <t>30001,180034</t>
@@ -723,12 +765,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1712,10 +1754,10 @@
         <v>20</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>18</v>
@@ -1726,19 +1768,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>18</v>
@@ -1749,19 +1791,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>18</v>
@@ -1772,7 +1814,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1781,13 +1823,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>18</v>
@@ -1798,7 +1840,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1807,13 +1849,13 @@
         <v>1</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>18</v>
@@ -1824,19 +1866,19 @@
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>18</v>
@@ -1847,19 +1889,19 @@
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>18</v>
@@ -1870,19 +1912,19 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>18</v>
@@ -1893,19 +1935,19 @@
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>18</v>
@@ -1916,7 +1958,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -1925,13 +1967,13 @@
         <v>2</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>18</v>
@@ -1942,7 +1984,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -1951,13 +1993,13 @@
         <v>2</v>
       </c>
       <c r="G17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="I17" s="10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>18</v>
@@ -1968,19 +2010,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>18</v>
@@ -1991,19 +2033,19 @@
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>18</v>
@@ -2014,19 +2056,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>18</v>
@@ -2037,19 +2079,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>18</v>
@@ -2060,7 +2102,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -2069,13 +2111,13 @@
         <v>3</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>18</v>
@@ -2086,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -2095,13 +2137,13 @@
         <v>3</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>18</v>
@@ -2112,19 +2154,19 @@
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>18</v>
@@ -2135,19 +2177,19 @@
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>18</v>
@@ -2158,19 +2200,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>18</v>
@@ -2181,19 +2223,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>18</v>
@@ -2204,7 +2246,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
@@ -2213,13 +2255,13 @@
         <v>4</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>18</v>
@@ -2230,7 +2272,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -2239,13 +2281,13 @@
         <v>4</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>18</v>
@@ -2256,19 +2298,19 @@
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>18</v>
@@ -2279,19 +2321,19 @@
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>18</v>
@@ -2302,19 +2344,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>18</v>
@@ -2325,19 +2367,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>18</v>
@@ -2348,7 +2390,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
@@ -2357,13 +2399,13 @@
         <v>5</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>18</v>
@@ -2374,7 +2416,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -2383,13 +2425,13 @@
         <v>5</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>18</v>
@@ -2400,19 +2442,19 @@
         <v>31</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>18</v>
@@ -2423,19 +2465,19 @@
         <v>32</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>18</v>
@@ -2446,19 +2488,19 @@
         <v>33</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>18</v>
@@ -2469,19 +2511,19 @@
         <v>34</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>18</v>
@@ -2492,7 +2534,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
@@ -2501,13 +2543,13 @@
         <v>6</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>18</v>
@@ -2518,7 +2560,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -2527,13 +2569,13 @@
         <v>6</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>16</v>
+        <v>130</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>18</v>
@@ -2544,7 +2586,7 @@
         <v>37</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E42" s="1">
         <v>7</v>
@@ -2555,7 +2597,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E43" s="1">
         <v>7</v>
@@ -2566,7 +2608,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E44" s="1">
         <v>7</v>
@@ -2577,7 +2619,7 @@
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
@@ -2588,7 +2630,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E46" s="1">
         <v>7</v>
@@ -2602,7 +2644,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E47" s="1">
         <v>7</v>
@@ -2616,7 +2658,7 @@
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E48" s="1">
         <v>8</v>
@@ -2627,7 +2669,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E49" s="1">
         <v>8</v>
@@ -2638,7 +2680,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
@@ -2649,7 +2691,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E51" s="1">
         <v>8</v>
@@ -2660,7 +2702,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E52" s="1">
         <v>8</v>
@@ -2674,7 +2716,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E53" s="1">
         <v>8</v>
@@ -2688,7 +2730,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E54" s="1">
         <v>9</v>
@@ -2699,7 +2741,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E55" s="1">
         <v>9</v>
@@ -2710,7 +2752,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E56" s="1">
         <v>9</v>
@@ -2721,7 +2763,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E57" s="1">
         <v>9</v>
@@ -2732,7 +2774,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E58" s="1">
         <v>9</v>
@@ -2746,7 +2788,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="E59" s="1">
         <v>9</v>
@@ -2760,7 +2802,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
@@ -2771,7 +2813,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E61" s="1">
         <v>10</v>
@@ -2782,7 +2824,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
@@ -2793,7 +2835,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E63" s="1">
         <v>10</v>
@@ -2804,7 +2846,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="E64" s="1">
         <v>10</v>
@@ -2818,7 +2860,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E65" s="1">
         <v>10</v>
@@ -2832,7 +2874,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E66" s="1">
         <v>11</v>
@@ -2843,7 +2885,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E67" s="1">
         <v>11</v>
@@ -2854,7 +2896,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="E68" s="1">
         <v>11</v>
@@ -2865,7 +2907,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -2876,7 +2918,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="E70" s="1">
         <v>11</v>
@@ -2890,7 +2932,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -2904,7 +2946,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="E72" s="1">
         <v>12</v>
@@ -2915,7 +2957,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E73" s="1">
         <v>12</v>
@@ -2926,7 +2968,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E74" s="1">
         <v>12</v>
@@ -2937,7 +2979,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E75" s="1">
         <v>12</v>
@@ -2948,7 +2990,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E76" s="1">
         <v>12</v>
@@ -2962,7 +3004,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E77" s="1">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -1819,9 +1819,7 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="9" t="s">
         <v>32</v>
       </c>
@@ -1963,9 +1961,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
+      <c r="F16" s="1"/>
       <c r="G16" s="9" t="s">
         <v>53</v>
       </c>
@@ -2107,9 +2103,7 @@
       <c r="E22" s="1">
         <v>3</v>
       </c>
-      <c r="F22" s="1">
-        <v>3</v>
-      </c>
+      <c r="F22" s="1"/>
       <c r="G22" s="9" t="s">
         <v>73</v>
       </c>
@@ -2251,9 +2245,7 @@
       <c r="E28" s="1">
         <v>4</v>
       </c>
-      <c r="F28" s="1">
-        <v>4</v>
-      </c>
+      <c r="F28" s="1"/>
       <c r="G28" s="9" t="s">
         <v>93</v>
       </c>
@@ -2395,9 +2387,7 @@
       <c r="E34" s="1">
         <v>5</v>
       </c>
-      <c r="F34" s="1">
-        <v>5</v>
-      </c>
+      <c r="F34" s="1"/>
       <c r="G34" s="9" t="s">
         <v>113</v>
       </c>
@@ -2539,9 +2529,7 @@
       <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="F40" s="1">
-        <v>6</v>
-      </c>
+      <c r="F40" s="1"/>
       <c r="G40" s="9" t="s">
         <v>133</v>
       </c>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -59,10 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="174">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="175">
   <si>
     <t>_Id</t>
   </si>
@@ -86,6 +83,12 @@
   </si>
   <si>
     <t>BaseRateList</t>
+  </si>
+  <si>
+    <t>DropRise</t>
+  </si>
+  <si>
+    <t>QualtityRise</t>
   </si>
   <si>
     <t>Id</t>
@@ -1609,112 +1612,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L77"/>
+  <dimension ref="C3:L77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="4" max="6" width="11.6272727272727" style="1" customWidth="1"/>
     <col min="7" max="7" width="42.7272727272727" style="1" customWidth="1"/>
     <col min="8" max="8" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.7272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.0909090909091" style="1" customWidth="1"/>
     <col min="10" max="10" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7272727272727" style="1" customWidth="1"/>
-    <col min="12" max="16380" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.0909090909091" style="1" customWidth="1"/>
+    <col min="12" max="12" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="13" max="16380" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="16381" max="16384" width="9.25454545454545" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:12">
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:12">
-      <c r="K2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="3" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:12">
@@ -1722,22 +1728,28 @@
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+      <c r="L6" s="1">
+        <v>100</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1745,22 +1757,30 @@
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K7" s="1">
+        <f t="shared" ref="K7:K26" si="0">K6-5</f>
+        <v>95</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" ref="L7:L26" si="1">L6-5</f>
+        <v>95</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:12">
@@ -1768,22 +1788,30 @@
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K8" s="1">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="1"/>
+        <v>90</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1791,22 +1819,30 @@
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="1"/>
+        <v>85</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
@@ -1814,23 +1850,30 @@
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="1"/>
       <c r="G10" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K10" s="1">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:12">
@@ -1838,7 +1881,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1847,16 +1890,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K11" s="1">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="1"/>
+        <v>75</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
@@ -1864,22 +1915,30 @@
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K12" s="1">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="1"/>
+        <v>70</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1887,22 +1946,30 @@
         <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K13" s="1">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="1"/>
+        <v>65</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -1910,22 +1977,30 @@
         <v>9</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K14" s="1">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -1933,22 +2008,30 @@
         <v>10</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="K15" s="1">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -1956,31 +2039,38 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="1"/>
       <c r="G16" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="I16" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
+      <c r="L16" s="1">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -1989,140 +2079,187 @@
         <v>2</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:12">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:12">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="L19" s="1">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:12">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:12">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
-      <c r="F22" s="1"/>
       <c r="G22" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K22" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -2131,140 +2268,181 @@
         <v>3</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K23" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:12">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" s="1">
         <v>4</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K24" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:12">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1">
         <v>4</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K25" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:12">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E26" s="1">
         <v>4</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:12">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E27" s="1">
         <v>4</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:12">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E28" s="1">
         <v>4</v>
       </c>
-      <c r="F28" s="1"/>
       <c r="G28" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -2273,140 +2451,175 @@
         <v>4</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30" s="1">
         <v>5</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E31" s="1">
         <v>5</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E32" s="1">
         <v>5</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E33" s="1">
         <v>5</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:12">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E34" s="1">
         <v>5</v>
       </c>
-      <c r="F34" s="1"/>
       <c r="G34" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:12">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -2415,140 +2628,175 @@
         <v>5</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:12">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:12">
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:12">
       <c r="C38" s="1">
         <v>33</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
       <c r="C39" s="1">
         <v>34</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:12">
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="F40" s="1"/>
       <c r="G40" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:12">
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -2557,68 +2805,74 @@
         <v>6</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:10">
+        <v>19</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
       <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E42" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="3:10">
+    <row r="43" customHeight="1" spans="3:12">
       <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E43" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:10">
+    <row r="44" customHeight="1" spans="3:12">
       <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E44" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="3:10">
+    <row r="45" customHeight="1" spans="3:12">
       <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E45" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="1">
         <v>41</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E46" s="1">
         <v>7</v>
@@ -2627,12 +2881,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:10">
+    <row r="47" customHeight="1" spans="3:12">
       <c r="C47" s="1">
         <v>42</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E47" s="1">
         <v>7</v>
@@ -2641,12 +2895,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="3:10">
+    <row r="48" customHeight="1" spans="3:12">
       <c r="C48" s="1">
         <v>43</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E48" s="1">
         <v>8</v>
@@ -2657,7 +2911,7 @@
         <v>44</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" s="1">
         <v>8</v>
@@ -2668,7 +2922,7 @@
         <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E50" s="1">
         <v>8</v>
@@ -2679,7 +2933,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E51" s="1">
         <v>8</v>
@@ -2690,7 +2944,7 @@
         <v>47</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E52" s="1">
         <v>8</v>
@@ -2704,7 +2958,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E53" s="1">
         <v>8</v>
@@ -2718,7 +2972,7 @@
         <v>49</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E54" s="1">
         <v>9</v>
@@ -2729,7 +2983,7 @@
         <v>50</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E55" s="1">
         <v>9</v>
@@ -2740,7 +2994,7 @@
         <v>51</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E56" s="1">
         <v>9</v>
@@ -2751,7 +3005,7 @@
         <v>52</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E57" s="1">
         <v>9</v>
@@ -2762,7 +3016,7 @@
         <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E58" s="1">
         <v>9</v>
@@ -2776,7 +3030,7 @@
         <v>54</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E59" s="1">
         <v>9</v>
@@ -2790,7 +3044,7 @@
         <v>55</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E60" s="1">
         <v>10</v>
@@ -2801,7 +3055,7 @@
         <v>56</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E61" s="1">
         <v>10</v>
@@ -2812,7 +3066,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
@@ -2823,7 +3077,7 @@
         <v>58</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E63" s="1">
         <v>10</v>
@@ -2834,7 +3088,7 @@
         <v>59</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E64" s="1">
         <v>10</v>
@@ -2848,7 +3102,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E65" s="1">
         <v>10</v>
@@ -2862,7 +3116,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E66" s="1">
         <v>11</v>
@@ -2873,7 +3127,7 @@
         <v>62</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E67" s="1">
         <v>11</v>
@@ -2884,7 +3138,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E68" s="1">
         <v>11</v>
@@ -2895,7 +3149,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E69" s="1">
         <v>11</v>
@@ -2906,7 +3160,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E70" s="1">
         <v>11</v>
@@ -2920,7 +3174,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -2934,7 +3188,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E72" s="1">
         <v>12</v>
@@ -2945,7 +3199,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E73" s="1">
         <v>12</v>
@@ -2956,7 +3210,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E74" s="1">
         <v>12</v>
@@ -2967,7 +3221,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75" s="1">
         <v>12</v>
@@ -2978,7 +3232,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E76" s="1">
         <v>12</v>
@@ -2992,7 +3246,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E77" s="1">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -768,23 +768,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1109,7 +1115,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1133,16 +1139,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1151,110 +1157,133 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1615,272 +1644,264 @@
   <dimension ref="C3:L77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="4" max="6" width="11.6272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="42.7272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.0909090909091" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="11" max="11" width="34.0909090909091" style="1" customWidth="1"/>
-    <col min="12" max="12" width="31.1818181818182" style="1" customWidth="1"/>
-    <col min="13" max="16380" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="16381" max="16384" width="9.25454545454545" style="1"/>
+    <col min="1" max="3" width="9.25454545454545" style="3" customWidth="1"/>
+    <col min="4" max="6" width="11.6272727272727" style="3" customWidth="1"/>
+    <col min="7" max="7" width="42.7272727272727" style="3" customWidth="1"/>
+    <col min="8" max="8" width="31.1818181818182" style="3" customWidth="1"/>
+    <col min="9" max="9" width="34.0909090909091" style="3" customWidth="1"/>
+    <col min="10" max="10" width="31.1818181818182" style="3" customWidth="1"/>
+    <col min="11" max="11" width="34.0909090909091" style="3" customWidth="1"/>
+    <col min="12" max="12" width="31.1818181818182" style="3" customWidth="1"/>
+    <col min="13" max="16380" width="9.25454545454545" style="3" customWidth="1"/>
+    <col min="16381" max="16384" width="9.25454545454545" style="3"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:12">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:12">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:12">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:12">
-      <c r="C6" s="1">
+      <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="J6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="3">
         <v>100</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
-      <c r="C7" s="1">
+      <c r="C7" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="1">
-        <f t="shared" ref="K7:K26" si="0">K6-5</f>
-        <v>95</v>
-      </c>
-      <c r="L7" s="1">
-        <f t="shared" ref="L7:L26" si="1">L6-5</f>
-        <v>95</v>
+      <c r="J7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="3">
+        <v>100</v>
+      </c>
+      <c r="L7" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:12">
-      <c r="C8" s="1">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="1">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="L8" s="1">
-        <f t="shared" si="1"/>
-        <v>90</v>
+      <c r="J8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="3">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
-      <c r="C9" s="1">
+      <c r="C9" s="3">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="1">
-        <f t="shared" si="0"/>
-        <v>85</v>
-      </c>
-      <c r="L9" s="1">
-        <f t="shared" si="1"/>
-        <v>85</v>
+      <c r="J9" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
-      <c r="C10" s="1">
+      <c r="C10" s="3">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="1">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="L10" s="1">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:12">
+      <c r="J10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="1">
@@ -1889,187 +1910,175 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="1">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="L11" s="1">
-        <f t="shared" si="1"/>
-        <v>75</v>
+      <c r="J11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="3">
+        <v>100</v>
+      </c>
+      <c r="L11" s="3">
+        <v>100</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
-      <c r="C12" s="1">
+      <c r="C12" s="3">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="1">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="1"/>
-        <v>70</v>
+      <c r="J12" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="3">
+        <v>80</v>
+      </c>
+      <c r="L12" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
-      <c r="C13" s="1">
+      <c r="C13" s="3">
         <v>8</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="1">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="L13" s="1">
-        <f t="shared" si="1"/>
-        <v>65</v>
+      <c r="J13" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="3">
+        <v>80</v>
+      </c>
+      <c r="L13" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
-      <c r="C14" s="1">
+      <c r="C14" s="3">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="3">
         <v>2</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="1">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="L14" s="1">
-        <f t="shared" si="1"/>
-        <v>60</v>
+      <c r="J14" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="3">
+        <v>80</v>
+      </c>
+      <c r="L14" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
-      <c r="C15" s="1">
+      <c r="C15" s="3">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="3">
         <v>2</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="1">
-        <f t="shared" si="0"/>
+      <c r="J15" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="3">
+        <v>80</v>
+      </c>
+      <c r="L15" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:12">
+      <c r="C16" s="3">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="L15" s="1">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:12">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="1">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="L16" s="1">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:12">
+      <c r="J16" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="3">
+        <v>80</v>
+      </c>
+      <c r="L16" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>12</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="1">
@@ -2078,187 +2087,175 @@
       <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="L17" s="1">
-        <f t="shared" si="1"/>
-        <v>45</v>
+      <c r="J17" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="3">
+        <v>80</v>
+      </c>
+      <c r="L17" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
-      <c r="C18" s="1">
+      <c r="C18" s="3">
         <v>13</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="L18" s="1">
-        <f t="shared" si="1"/>
-        <v>40</v>
+      <c r="J18" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="3">
+        <v>60</v>
+      </c>
+      <c r="L18" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
-      <c r="C19" s="1">
+      <c r="C19" s="3">
         <v>14</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="3">
         <v>3</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="L19" s="1">
-        <f t="shared" si="1"/>
-        <v>35</v>
+      <c r="J19" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="3">
+        <v>60</v>
+      </c>
+      <c r="L19" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
-      <c r="C20" s="1">
+      <c r="C20" s="3">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="3">
         <v>3</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="J20" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="L20" s="1">
-        <f t="shared" si="1"/>
-        <v>30</v>
+      <c r="J20" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="3">
+        <v>60</v>
+      </c>
+      <c r="L20" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
-      <c r="C21" s="1">
+      <c r="C21" s="3">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="3">
         <v>3</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="J21" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="1">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="L21" s="1">
-        <f t="shared" si="1"/>
-        <v>25</v>
+      <c r="J21" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="3">
+        <v>60</v>
+      </c>
+      <c r="L21" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:12">
-      <c r="C22" s="1">
+      <c r="C22" s="3">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="3">
         <v>3</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="L22" s="1">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:12">
+      <c r="J22" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="3">
+        <v>60</v>
+      </c>
+      <c r="L22" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C23" s="1">
         <v>18</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E23" s="1">
@@ -2267,181 +2264,175 @@
       <c r="F23" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="L23" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:12">
-      <c r="C24" s="1">
-        <v>19</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="J23" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="3">
+        <v>60</v>
+      </c>
+      <c r="L23" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C24" s="2">
+        <v>19</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L24" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
+      <c r="J24" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="3">
+        <v>40</v>
+      </c>
+      <c r="L24" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
-      <c r="C25" s="1">
+      <c r="C25" s="3">
         <v>20</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="3">
         <v>4</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L25" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
+      <c r="J25" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="3">
+        <v>40</v>
+      </c>
+      <c r="L25" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
-      <c r="C26" s="1">
+      <c r="C26" s="3">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="3">
         <v>4</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
+      <c r="J26" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="3">
+        <v>40</v>
+      </c>
+      <c r="L26" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:12">
-      <c r="C27" s="1">
+      <c r="C27" s="3">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="3">
         <v>4</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
+      <c r="J27" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="3">
+        <v>40</v>
+      </c>
+      <c r="L27" s="3">
+        <v>40</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
-      <c r="C28" s="1">
+      <c r="C28" s="3">
         <v>23</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="3">
         <v>4</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="J28" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:12">
+      <c r="J28" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="3">
+        <v>40</v>
+      </c>
+      <c r="L28" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E29" s="1">
@@ -2450,175 +2441,175 @@
       <c r="F29" s="1">
         <v>4</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:12">
-      <c r="C30" s="1">
+      <c r="J29" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="3">
+        <v>40</v>
+      </c>
+      <c r="L29" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C30" s="2">
         <v>25</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>5</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
+      <c r="J30" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="3">
+        <v>20</v>
+      </c>
+      <c r="L30" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:12">
-      <c r="C31" s="1">
+      <c r="C31" s="3">
         <v>26</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
+      <c r="J31" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="3">
+        <v>20</v>
+      </c>
+      <c r="L31" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:12">
-      <c r="C32" s="1">
+      <c r="C32" s="3">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="3">
         <v>5</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="J32" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
+      <c r="J32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="3">
+        <v>20</v>
+      </c>
+      <c r="L32" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:12">
-      <c r="C33" s="1">
+      <c r="C33" s="3">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="3">
         <v>5</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="J33" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
+      <c r="J33" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="3">
+        <v>20</v>
+      </c>
+      <c r="L33" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:12">
-      <c r="C34" s="1">
+      <c r="C34" s="3">
         <v>29</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="3">
         <v>5</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J34" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:12">
+      <c r="J34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="3">
+        <v>20</v>
+      </c>
+      <c r="L34" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="13" t="s">
         <v>116</v>
       </c>
       <c r="E35" s="1">
@@ -2627,175 +2618,175 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" s="1">
+      <c r="J35" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="3">
+        <v>20</v>
+      </c>
+      <c r="L35" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:12">
+      <c r="C36" s="3">
+        <v>31</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" s="3">
+        <v>6</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="3">
         <v>0</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L36" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:12">
-      <c r="C36" s="1">
-        <v>31</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" s="1">
+    <row r="37" customHeight="1" spans="3:12">
+      <c r="C37" s="3">
+        <v>32</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="3">
         <v>6</v>
       </c>
-      <c r="G36" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="H36" s="9" t="s">
+      <c r="G37" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I36" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="1">
+      <c r="I37" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="3">
         <v>0</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L37" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:12">
-      <c r="C37" s="1">
-        <v>32</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="1">
+    <row r="38" customHeight="1" spans="3:12">
+      <c r="C38" s="3">
+        <v>33</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="3">
         <v>6</v>
       </c>
-      <c r="G37" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H37" s="9" t="s">
+      <c r="G38" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="H38" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I37" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="1">
+      <c r="I38" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="3">
         <v>0</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L38" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:12">
-      <c r="C38" s="1">
-        <v>33</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" s="1">
+    <row r="39" customHeight="1" spans="3:12">
+      <c r="C39" s="3">
+        <v>34</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="3">
         <v>6</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K38" s="1">
+      <c r="G39" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="J39" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="3">
         <v>0</v>
       </c>
-      <c r="L38" s="1">
+      <c r="L39" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:12">
-      <c r="C39" s="1">
-        <v>34</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E39" s="1">
+    <row r="40" customHeight="1" spans="3:12">
+      <c r="C40" s="3">
+        <v>35</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" s="3">
         <v>6</v>
       </c>
-      <c r="G39" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H39" s="9" t="s">
+      <c r="G40" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="I39" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39" s="1">
+      <c r="I40" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="J40" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="3">
         <v>0</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L40" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:12">
-      <c r="C40" s="1">
-        <v>35</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E40" s="1">
-        <v>6</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:12">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="16" t="s">
         <v>136</v>
       </c>
       <c r="E41" s="1">
@@ -2804,16 +2795,16 @@
       <c r="F41" s="1">
         <v>6</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="20" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="1">
@@ -2824,434 +2815,434 @@
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:12">
-      <c r="C42" s="1">
+      <c r="C42" s="3">
         <v>37</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:12">
-      <c r="C43" s="1">
+      <c r="C43" s="3">
         <v>38</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:12">
-      <c r="C44" s="1">
+      <c r="C44" s="3">
         <v>39</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:12">
-      <c r="C45" s="1">
+      <c r="C45" s="3">
         <v>40</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C46" s="1">
+    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="3">
         <v>41</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="3">
         <v>7</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:12">
-      <c r="C47" s="1">
+      <c r="C47" s="3">
         <v>42</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="3">
         <v>7</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:12">
-      <c r="C48" s="1">
+      <c r="C48" s="3">
         <v>43</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
-      <c r="C49" s="1">
+      <c r="C49" s="3">
         <v>44</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
-      <c r="C50" s="1">
+      <c r="C50" s="3">
         <v>45</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
-      <c r="C51" s="1">
+      <c r="C51" s="3">
         <v>46</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
-      <c r="C52" s="1">
+      <c r="C52" s="3">
         <v>47</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="3">
         <v>8</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
-      <c r="C53" s="1">
+      <c r="C53" s="3">
         <v>48</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="3">
         <v>8</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
-      <c r="C54" s="1">
+      <c r="C54" s="3">
         <v>49</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
-      <c r="C55" s="1">
+      <c r="C55" s="3">
         <v>50</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
-      <c r="C56" s="1">
+      <c r="C56" s="3">
         <v>51</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
-      <c r="C57" s="1">
+      <c r="C57" s="3">
         <v>52</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
-      <c r="C58" s="1">
+      <c r="C58" s="3">
         <v>53</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="3">
         <v>9</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
-      <c r="C59" s="1">
+      <c r="C59" s="3">
         <v>54</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="3">
         <v>9</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="3">
         <v>9</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
-      <c r="C60" s="1">
+      <c r="C60" s="3">
         <v>55</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
-      <c r="C61" s="1">
+      <c r="C61" s="3">
         <v>56</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
-      <c r="C62" s="1">
+      <c r="C62" s="3">
         <v>57</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
-      <c r="C63" s="1">
+      <c r="C63" s="3">
         <v>58</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
-      <c r="C64" s="1">
+      <c r="C64" s="3">
         <v>59</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64" s="3">
         <v>10</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
-      <c r="C65" s="1">
+      <c r="C65" s="3">
         <v>60</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="3">
         <v>10</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
-      <c r="C66" s="1">
+      <c r="C66" s="3">
         <v>61</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
-      <c r="C67" s="1">
+      <c r="C67" s="3">
         <v>62</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
-      <c r="C68" s="1">
+      <c r="C68" s="3">
         <v>63</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
-      <c r="C69" s="1">
+      <c r="C69" s="3">
         <v>64</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
-      <c r="C70" s="1">
+      <c r="C70" s="3">
         <v>65</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70" s="3">
         <v>11</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
-      <c r="C71" s="1">
+      <c r="C71" s="3">
         <v>66</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="3">
         <v>11</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="3">
         <v>11</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
-      <c r="C72" s="1">
+      <c r="C72" s="3">
         <v>67</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
-      <c r="C73" s="1">
+      <c r="C73" s="3">
         <v>68</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
-      <c r="C74" s="1">
+      <c r="C74" s="3">
         <v>69</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
-      <c r="C75" s="1">
+      <c r="C75" s="3">
         <v>70</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
-      <c r="C76" s="1">
+      <c r="C76" s="3">
         <v>71</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76" s="3">
         <v>12</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76" s="3">
         <v>12</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
-      <c r="C77" s="1">
+      <c r="C77" s="3">
         <v>72</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77" s="3">
         <v>12</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77" s="3">
         <v>12</v>
       </c>
     </row>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -768,12 +768,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1239,7 +1239,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1256,13 +1256,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1762,16 +1756,16 @@
       <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="3">
@@ -1791,16 +1785,16 @@
       <c r="E7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="3">
@@ -1820,16 +1814,16 @@
       <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="3">
@@ -1849,16 +1843,16 @@
       <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="3">
@@ -1878,16 +1872,16 @@
       <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="3">
@@ -1910,16 +1904,16 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="18" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="3">
@@ -1939,16 +1933,16 @@
       <c r="E12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="3">
@@ -1968,16 +1962,16 @@
       <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="3">
@@ -1997,16 +1991,16 @@
       <c r="E14" s="3">
         <v>2</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J14" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="3">
@@ -2026,16 +2020,16 @@
       <c r="E15" s="3">
         <v>2</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="3">
@@ -2055,16 +2049,16 @@
       <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="19" t="s">
+      <c r="I16" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J16" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="3">
@@ -2087,16 +2081,16 @@
       <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="18" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="3">
@@ -2116,16 +2110,16 @@
       <c r="E18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J18" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="3">
@@ -2145,16 +2139,16 @@
       <c r="E19" s="3">
         <v>3</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I19" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J19" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="3">
@@ -2174,16 +2168,16 @@
       <c r="E20" s="3">
         <v>3</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="19" t="s">
+      <c r="I20" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="J20" s="18" t="s">
+      <c r="J20" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="3">
@@ -2203,16 +2197,16 @@
       <c r="E21" s="3">
         <v>3</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="19" t="s">
+      <c r="I21" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J21" s="18" t="s">
+      <c r="J21" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="3">
@@ -2232,16 +2226,16 @@
       <c r="E22" s="3">
         <v>3</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="I22" s="19" t="s">
+      <c r="I22" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="18" t="s">
+      <c r="J22" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="3">
@@ -2264,16 +2258,16 @@
       <c r="F23" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="21" t="s">
+      <c r="I23" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="18" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="3">
@@ -2287,22 +2281,22 @@
       <c r="C24" s="2">
         <v>19</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="5" t="s">
         <v>79</v>
       </c>
       <c r="E24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="J24" s="22" t="s">
+      <c r="J24" s="20" t="s">
         <v>19</v>
       </c>
       <c r="K24" s="3">
@@ -2322,16 +2316,16 @@
       <c r="E25" s="3">
         <v>4</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="I25" s="19" t="s">
+      <c r="I25" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="18" t="s">
+      <c r="J25" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="3">
@@ -2351,16 +2345,16 @@
       <c r="E26" s="3">
         <v>4</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="I26" s="19" t="s">
+      <c r="I26" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="J26" s="18" t="s">
+      <c r="J26" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="3">
@@ -2380,16 +2374,16 @@
       <c r="E27" s="3">
         <v>4</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="18" t="s">
+      <c r="H27" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="18" t="s">
+      <c r="J27" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="3">
@@ -2409,16 +2403,16 @@
       <c r="E28" s="3">
         <v>4</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="18" t="s">
+      <c r="H28" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="J28" s="18" t="s">
+      <c r="J28" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="3">
@@ -2441,16 +2435,16 @@
       <c r="F29" s="1">
         <v>4</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="J29" s="20" t="s">
+      <c r="J29" s="18" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="3">
@@ -2464,22 +2458,22 @@
       <c r="C30" s="2">
         <v>25</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="I30" s="23" t="s">
+      <c r="I30" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="20" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="3">
@@ -2499,16 +2493,16 @@
       <c r="E31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="18" t="s">
+      <c r="G31" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H31" s="18" t="s">
+      <c r="H31" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="19" t="s">
+      <c r="I31" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="J31" s="18" t="s">
+      <c r="J31" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K31" s="3">
@@ -2528,16 +2522,16 @@
       <c r="E32" s="3">
         <v>5</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="18" t="s">
+      <c r="H32" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="19" t="s">
+      <c r="I32" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="J32" s="18" t="s">
+      <c r="J32" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K32" s="3">
@@ -2557,16 +2551,16 @@
       <c r="E33" s="3">
         <v>5</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="H33" s="18" t="s">
+      <c r="H33" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I33" s="19" t="s">
+      <c r="I33" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="J33" s="18" t="s">
+      <c r="J33" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="3">
@@ -2586,16 +2580,16 @@
       <c r="E34" s="3">
         <v>5</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="18" t="s">
+      <c r="H34" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I34" s="19" t="s">
+      <c r="I34" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="J34" s="18" t="s">
+      <c r="J34" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="3">
@@ -2609,7 +2603,7 @@
       <c r="C35" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="11" t="s">
         <v>116</v>
       </c>
       <c r="E35" s="1">
@@ -2618,16 +2612,16 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="G35" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H35" s="20" t="s">
+      <c r="H35" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I35" s="21" t="s">
+      <c r="I35" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="J35" s="20" t="s">
+      <c r="J35" s="18" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="3">
@@ -2641,22 +2635,22 @@
       <c r="C36" s="3">
         <v>31</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="12" t="s">
         <v>119</v>
       </c>
       <c r="E36" s="3">
         <v>6</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G36" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="H36" s="18" t="s">
+      <c r="H36" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I36" s="19" t="s">
+      <c r="I36" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="J36" s="18" t="s">
+      <c r="J36" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="3">
@@ -2670,22 +2664,22 @@
       <c r="C37" s="3">
         <v>32</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="12" t="s">
         <v>123</v>
       </c>
       <c r="E37" s="3">
         <v>6</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="H37" s="18" t="s">
+      <c r="H37" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="J37" s="18" t="s">
+      <c r="J37" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="3">
@@ -2699,22 +2693,22 @@
       <c r="C38" s="3">
         <v>33</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="12" t="s">
         <v>126</v>
       </c>
       <c r="E38" s="3">
         <v>6</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="H38" s="18" t="s">
+      <c r="H38" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="J38" s="18" t="s">
+      <c r="J38" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="3">
@@ -2728,22 +2722,22 @@
       <c r="C39" s="3">
         <v>34</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>129</v>
       </c>
       <c r="E39" s="3">
         <v>6</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="H39" s="18" t="s">
+      <c r="H39" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="I39" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="J39" s="18" t="s">
+      <c r="J39" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="3">
@@ -2757,22 +2751,22 @@
       <c r="C40" s="3">
         <v>35</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="13" t="s">
         <v>133</v>
       </c>
       <c r="E40" s="3">
         <v>6</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="H40" s="18" t="s">
+      <c r="H40" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="I40" s="19" t="s">
+      <c r="I40" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="J40" s="18" t="s">
+      <c r="J40" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="3">
@@ -2786,7 +2780,7 @@
       <c r="C41" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="14" t="s">
         <v>136</v>
       </c>
       <c r="E41" s="1">
@@ -2795,16 +2789,16 @@
       <c r="F41" s="1">
         <v>6</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="I41" s="21" t="s">
+      <c r="I41" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="J41" s="20" t="s">
+      <c r="J41" s="18" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="1">
@@ -2862,7 +2856,7 @@
       <c r="C46" s="3">
         <v>41</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="15" t="s">
         <v>143</v>
       </c>
       <c r="E46" s="3">
@@ -2923,7 +2917,7 @@
       <c r="C51" s="3">
         <v>46</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="15" t="s">
         <v>148</v>
       </c>
       <c r="E51" s="3">
@@ -3117,7 +3111,7 @@
       <c r="C67" s="3">
         <v>62</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="15" t="s">
         <v>164</v>
       </c>
       <c r="E67" s="3">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -301,10 +306,10 @@
     <t>魅惑花园</t>
   </si>
   <si>
-    <t>2019,4007,5004</t>
-  </si>
-  <si>
-    <t>24,6000,6000</t>
+    <t>2019,4007,5004,3001</t>
+  </si>
+  <si>
+    <t>24,6000,6000,10000</t>
   </si>
   <si>
     <t>30001,180019</t>
@@ -313,7 +318,7 @@
     <t>藤蔓密道</t>
   </si>
   <si>
-    <t>2020,4007,5004</t>
+    <t>2020,4007,5004,3001</t>
   </si>
   <si>
     <t>30001,180020</t>
@@ -322,7 +327,7 @@
     <t>黑水潭</t>
   </si>
   <si>
-    <t>2021,4007,5004</t>
+    <t>2021,4007,5004,3001</t>
   </si>
   <si>
     <t>30001,180021</t>
@@ -331,10 +336,10 @@
     <t>望月高台</t>
   </si>
   <si>
-    <t>2022,4007,5004</t>
-  </si>
-  <si>
-    <t>25,6000,6000</t>
+    <t>2022,4007,5004,3001</t>
+  </si>
+  <si>
+    <t>25,6000,6000,10000</t>
   </si>
   <si>
     <t>30001,180022</t>
@@ -343,7 +348,7 @@
     <t>毒瘴山谷</t>
   </si>
   <si>
-    <t>2023,4007,5004</t>
+    <t>2023,4007,5004,3001</t>
   </si>
   <si>
     <t>30001,180023</t>
@@ -352,7 +357,7 @@
     <t>梦境之树</t>
   </si>
   <si>
-    <t>2024,4007,5004</t>
+    <t>2024,4007,5004,3001</t>
   </si>
   <si>
     <t>30001,180024</t>
@@ -361,10 +366,10 @@
     <t>荒漠边缘</t>
   </si>
   <si>
-    <t>2025,4007,5005</t>
-  </si>
-  <si>
-    <t>26,6000,6000</t>
+    <t>2025,4007,5005,3002</t>
+  </si>
+  <si>
+    <t>26,6000,6000,10000</t>
   </si>
   <si>
     <t>30001,180025</t>
@@ -373,7 +378,7 @@
     <t>遗忘高地</t>
   </si>
   <si>
-    <t>2026,4007,5005</t>
+    <t>2026,4007,5005,3002</t>
   </si>
   <si>
     <t>30001,180026</t>
@@ -382,7 +387,7 @@
     <t>遗弃坟场</t>
   </si>
   <si>
-    <t>2027,4007,5005</t>
+    <t>2027,4007,5005,3002</t>
   </si>
   <si>
     <t>30001,180027</t>
@@ -391,10 +396,10 @@
     <t>幽暗灵墓</t>
   </si>
   <si>
-    <t>2028,4007,5005</t>
-  </si>
-  <si>
-    <t>27,6000,6000</t>
+    <t>2028,4007,5005,3002</t>
+  </si>
+  <si>
+    <t>27,6000,6000,10000</t>
   </si>
   <si>
     <t>30001,180028</t>
@@ -403,7 +408,7 @@
     <t>亡者塔楼</t>
   </si>
   <si>
-    <t>2029,4007,5005</t>
+    <t>2029,4007,5005,3002</t>
   </si>
   <si>
     <t>30001,180029</t>
@@ -412,7 +417,7 @@
     <t>埋骨之地</t>
   </si>
   <si>
-    <t>2030,4007,5005</t>
+    <t>2030,4007,5005,3002</t>
   </si>
   <si>
     <t>30001,180030</t>
@@ -421,10 +426,10 @@
     <t>蛮鬃外围</t>
   </si>
   <si>
-    <t>2031,4007,5006</t>
-  </si>
-  <si>
-    <t>28,6000,6000</t>
+    <t>2031,4007,5006,3003</t>
+  </si>
+  <si>
+    <t>28,6000,6000,10000</t>
   </si>
   <si>
     <t>30001,180031</t>
@@ -433,7 +438,7 @@
     <t>荆棘围栏</t>
   </si>
   <si>
-    <t>2032,4007,5006</t>
+    <t>2032,4007,5006,3003</t>
   </si>
   <si>
     <t>30001,180032</t>
@@ -442,7 +447,7 @@
     <t>碎石校场</t>
   </si>
   <si>
-    <t>2033,4007,5006</t>
+    <t>2033,4007,5006,3003</t>
   </si>
   <si>
     <t>30001,180033</t>
@@ -451,10 +456,10 @@
     <t>图腾祭坛</t>
   </si>
   <si>
-    <t>2034,4007,5006</t>
-  </si>
-  <si>
-    <t>29,6000,6000</t>
+    <t>2034,4007,5006,3003</t>
+  </si>
+  <si>
+    <t>29,6000,6000,10000</t>
   </si>
   <si>
     <t>30001,180034</t>
@@ -463,7 +468,7 @@
     <t>觐见之路</t>
   </si>
   <si>
-    <t>2035,4007,5006</t>
+    <t>2035,4007,5006,3003</t>
   </si>
   <si>
     <t>30001,180035</t>
@@ -472,7 +477,7 @@
     <t>钢鬃王座</t>
   </si>
   <si>
-    <t>2036,4007,5006</t>
+    <t>2036,4007,5006,3003</t>
   </si>
   <si>
     <t>30001,180036</t>
@@ -768,12 +773,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -773,12 +773,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1951,10 +1951,10 @@
         <v>19</v>
       </c>
       <c r="K12" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L12" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1980,10 +1980,10 @@
         <v>19</v>
       </c>
       <c r="K13" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L13" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -2009,10 +2009,10 @@
         <v>19</v>
       </c>
       <c r="K14" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L14" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -2038,10 +2038,10 @@
         <v>19</v>
       </c>
       <c r="K15" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -2067,10 +2067,10 @@
         <v>19</v>
       </c>
       <c r="K16" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L16" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2099,10 +2099,10 @@
         <v>19</v>
       </c>
       <c r="K17" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L17" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
@@ -2128,10 +2128,10 @@
         <v>19</v>
       </c>
       <c r="K18" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L18" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
@@ -2157,10 +2157,10 @@
         <v>19</v>
       </c>
       <c r="K19" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L19" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
@@ -2186,10 +2186,10 @@
         <v>19</v>
       </c>
       <c r="K20" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
@@ -2215,10 +2215,10 @@
         <v>19</v>
       </c>
       <c r="K21" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L21" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:12">
@@ -2244,10 +2244,10 @@
         <v>19</v>
       </c>
       <c r="K22" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2276,10 +2276,10 @@
         <v>19</v>
       </c>
       <c r="K23" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L23" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -2305,10 +2305,10 @@
         <v>19</v>
       </c>
       <c r="K24" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L24" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
@@ -2334,10 +2334,10 @@
         <v>19</v>
       </c>
       <c r="K25" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L25" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
@@ -2363,10 +2363,10 @@
         <v>19</v>
       </c>
       <c r="K26" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L26" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:12">
@@ -2392,10 +2392,10 @@
         <v>19</v>
       </c>
       <c r="K27" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L27" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
@@ -2421,10 +2421,10 @@
         <v>19</v>
       </c>
       <c r="K28" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L28" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2453,10 +2453,10 @@
         <v>19</v>
       </c>
       <c r="K29" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L29" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12">
@@ -2482,10 +2482,10 @@
         <v>19</v>
       </c>
       <c r="K30" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L30" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:12">
@@ -2511,10 +2511,10 @@
         <v>19</v>
       </c>
       <c r="K31" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L31" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:12">
@@ -2540,10 +2540,10 @@
         <v>19</v>
       </c>
       <c r="K32" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L32" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:12">
@@ -2569,10 +2569,10 @@
         <v>19</v>
       </c>
       <c r="K33" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L33" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:12">
@@ -2598,10 +2598,10 @@
         <v>19</v>
       </c>
       <c r="K34" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L34" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2630,10 +2630,10 @@
         <v>19</v>
       </c>
       <c r="K35" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="L35" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:12">
@@ -2659,10 +2659,10 @@
         <v>19</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L36" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:12">
@@ -2688,10 +2688,10 @@
         <v>19</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L37" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:12">
@@ -2717,10 +2717,10 @@
         <v>19</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L38" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:12">
@@ -2746,10 +2746,10 @@
         <v>19</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L39" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:12">
@@ -2775,10 +2775,10 @@
         <v>19</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L40" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2806,11 +2806,11 @@
       <c r="J41" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
-        <v>0</v>
+      <c r="K41" s="3">
+        <v>80</v>
+      </c>
+      <c r="L41" s="3">
+        <v>80</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:12">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="194">
   <si>
     <t>_Id</t>
   </si>
@@ -486,37 +486,94 @@
     <t>地穴入口</t>
   </si>
   <si>
+    <t>2037,4007,5007,3003</t>
+  </si>
+  <si>
+    <t>30,6000,6000,10000</t>
+  </si>
+  <si>
+    <t>30001,180037</t>
+  </si>
+  <si>
     <t>幽火隧道</t>
   </si>
   <si>
+    <t>2038,4007,5007,3003</t>
+  </si>
+  <si>
+    <t>30001,180038</t>
+  </si>
+  <si>
     <t>岩浆裂隙</t>
   </si>
   <si>
+    <t>2039,4007,5007,3003</t>
+  </si>
+  <si>
+    <t>30001,180039</t>
+  </si>
+  <si>
     <t>烈焰围栏</t>
   </si>
   <si>
+    <t>2040,4007,5007,3003</t>
+  </si>
+  <si>
+    <t>30001,180040</t>
+  </si>
+  <si>
     <t>焰姬大厅</t>
   </si>
   <si>
+    <t>2041,4007,5007,3003</t>
+  </si>
+  <si>
+    <t>30001,180041</t>
+  </si>
+  <si>
     <t>地心熔炉</t>
   </si>
   <si>
+    <t>2042,4007,5007,3003</t>
+  </si>
+  <si>
+    <t>30001,180042</t>
+  </si>
+  <si>
     <t>永冻墓道</t>
   </si>
   <si>
+    <t>2043,4007,5008,3004</t>
+  </si>
+  <si>
     <t>冰冷大厅</t>
   </si>
   <si>
+    <t>2044,4007,5008,3004</t>
+  </si>
+  <si>
     <t>寒冰湖岸</t>
   </si>
   <si>
+    <t>2045,4007,5008,3004</t>
+  </si>
+  <si>
     <t>冰霜平原</t>
   </si>
   <si>
+    <t>2046,4007,5008,3004</t>
+  </si>
+  <si>
     <t>冰霜高地</t>
   </si>
   <si>
+    <t>2047,4007,5008,3004</t>
+  </si>
+  <si>
     <t>凛冽王宫</t>
+  </si>
+  <si>
+    <t>2048,4007,5008,3004</t>
   </si>
   <si>
     <t>鬼眼蛛巢</t>
@@ -1244,7 +1301,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1274,6 +1331,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1282,6 +1340,7 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1761,16 +1820,16 @@
       <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="3">
@@ -1790,16 +1849,16 @@
       <c r="E7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="3">
@@ -1819,16 +1878,16 @@
       <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="3">
@@ -1848,16 +1907,16 @@
       <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="3">
@@ -1877,16 +1936,16 @@
       <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="3">
@@ -1909,16 +1968,16 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="3">
@@ -1938,16 +1997,16 @@
       <c r="E12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="3">
@@ -1967,16 +2026,16 @@
       <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="3">
@@ -1996,16 +2055,16 @@
       <c r="E14" s="3">
         <v>2</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="3">
@@ -2025,16 +2084,16 @@
       <c r="E15" s="3">
         <v>2</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="3">
@@ -2054,16 +2113,16 @@
       <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="3">
@@ -2086,16 +2145,16 @@
       <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="3">
@@ -2115,16 +2174,16 @@
       <c r="E18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="3">
@@ -2144,16 +2203,16 @@
       <c r="E19" s="3">
         <v>3</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="3">
@@ -2173,16 +2232,16 @@
       <c r="E20" s="3">
         <v>3</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="3">
@@ -2202,16 +2261,16 @@
       <c r="E21" s="3">
         <v>3</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="3">
@@ -2231,16 +2290,16 @@
       <c r="E22" s="3">
         <v>3</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="3">
@@ -2263,16 +2322,16 @@
       <c r="F23" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="H23" s="18" t="s">
+      <c r="H23" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="19" t="s">
+      <c r="I23" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="J23" s="18" t="s">
+      <c r="J23" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="3">
@@ -2292,16 +2351,16 @@
       <c r="E24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="H24" s="20" t="s">
+      <c r="G24" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="21" t="s">
         <v>19</v>
       </c>
       <c r="K24" s="3">
@@ -2321,16 +2380,16 @@
       <c r="E25" s="3">
         <v>4</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="J25" s="16" t="s">
+      <c r="J25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="3">
@@ -2350,16 +2409,16 @@
       <c r="E26" s="3">
         <v>4</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="3">
@@ -2379,16 +2438,16 @@
       <c r="E27" s="3">
         <v>4</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J27" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="3">
@@ -2408,16 +2467,16 @@
       <c r="E28" s="3">
         <v>4</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="3">
@@ -2440,16 +2499,16 @@
       <c r="F29" s="1">
         <v>4</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="H29" s="18" t="s">
+      <c r="H29" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="J29" s="18" t="s">
+      <c r="J29" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="3">
@@ -2469,16 +2528,16 @@
       <c r="E30" s="2">
         <v>5</v>
       </c>
-      <c r="G30" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" s="20" t="s">
+      <c r="G30" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J30" s="20" t="s">
+      <c r="J30" s="21" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="3">
@@ -2498,16 +2557,16 @@
       <c r="E31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="J31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K31" s="3">
@@ -2527,16 +2586,16 @@
       <c r="E32" s="3">
         <v>5</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K32" s="3">
@@ -2556,16 +2615,16 @@
       <c r="E33" s="3">
         <v>5</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="3">
@@ -2585,16 +2644,16 @@
       <c r="E34" s="3">
         <v>5</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="J34" s="16" t="s">
+      <c r="J34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="3">
@@ -2617,16 +2676,16 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="H35" s="18" t="s">
+      <c r="H35" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="J35" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="3">
@@ -2646,16 +2705,16 @@
       <c r="E36" s="3">
         <v>6</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="J36" s="16" t="s">
+      <c r="J36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="3">
@@ -2675,16 +2734,16 @@
       <c r="E37" s="3">
         <v>6</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="3">
@@ -2704,16 +2763,16 @@
       <c r="E38" s="3">
         <v>6</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="J38" s="16" t="s">
+      <c r="J38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="3">
@@ -2733,16 +2792,16 @@
       <c r="E39" s="3">
         <v>6</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="J39" s="16" t="s">
+      <c r="J39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="3">
@@ -2762,16 +2821,16 @@
       <c r="E40" s="3">
         <v>6</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="I40" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="J40" s="16" t="s">
+      <c r="J40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="3">
@@ -2794,16 +2853,16 @@
       <c r="F41" s="1">
         <v>6</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="H41" s="18" t="s">
+      <c r="H41" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="I41" s="19" t="s">
+      <c r="I41" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="J41" s="18" t="s">
+      <c r="J41" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="3">
@@ -2823,16 +2882,52 @@
       <c r="E42" s="3">
         <v>7</v>
       </c>
+      <c r="G42" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="3">
+        <v>60</v>
+      </c>
+      <c r="L42" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="3:12">
       <c r="C43" s="3">
         <v>38</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E43" s="3">
         <v>7</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="3">
+        <v>60</v>
+      </c>
+      <c r="L43" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:12">
@@ -2840,10 +2935,28 @@
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E44" s="3">
         <v>7</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I44" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="3">
+        <v>60</v>
+      </c>
+      <c r="L44" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:12">
@@ -2851,24 +2964,58 @@
         <v>40</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E45" s="3">
         <v>7</v>
+      </c>
+      <c r="G45" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="3">
+        <v>60</v>
+      </c>
+      <c r="L45" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="3">
         <v>41</v>
       </c>
-      <c r="D46" s="15" t="s">
-        <v>143</v>
+      <c r="D46" s="16" t="s">
+        <v>152</v>
       </c>
       <c r="E46" s="3">
         <v>7</v>
       </c>
-      <c r="F46" s="3">
-        <v>7</v>
+      <c r="F46" s="3"/>
+      <c r="G46" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="I46" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="3">
+        <v>60</v>
+      </c>
+      <c r="L46" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:12">
@@ -2876,13 +3023,31 @@
         <v>42</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E47" s="3">
         <v>7</v>
       </c>
       <c r="F47" s="3">
         <v>7</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="3">
+        <v>60</v>
+      </c>
+      <c r="L47" s="3">
+        <v>60</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:12">
@@ -2890,65 +3055,78 @@
         <v>43</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E48" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:6">
+      <c r="G48" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:7">
       <c r="C49" s="3">
         <v>44</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="E49" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:6">
+      <c r="G49" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:7">
       <c r="C50" s="3">
         <v>45</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="E50" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:6">
+      <c r="G50" s="17" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:7">
       <c r="C51" s="3">
         <v>46</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>148</v>
+      <c r="D51" s="16" t="s">
+        <v>164</v>
       </c>
       <c r="E51" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:6">
+      <c r="G51" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:7">
       <c r="C52" s="3">
         <v>47</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="E52" s="3">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:6">
+      <c r="F52" s="3"/>
+      <c r="G52" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:7">
       <c r="C53" s="3">
         <v>48</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E53" s="3">
         <v>8</v>
@@ -2956,71 +3134,71 @@
       <c r="F53" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:6">
+      <c r="G53" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:7">
       <c r="C54" s="3">
         <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="E54" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:6">
+    <row r="55" customHeight="1" spans="3:7">
       <c r="C55" s="3">
         <v>50</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="E55" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="3:6">
+    <row r="56" customHeight="1" spans="3:7">
       <c r="C56" s="3">
         <v>51</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="E56" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:6">
+    <row r="57" customHeight="1" spans="3:7">
       <c r="C57" s="3">
         <v>52</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="E57" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:6">
+    <row r="58" customHeight="1" spans="3:7">
       <c r="C58" s="3">
         <v>53</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="E58" s="3">
         <v>9</v>
       </c>
-      <c r="F58" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:6">
+    </row>
+    <row r="59" customHeight="1" spans="3:7">
       <c r="C59" s="3">
         <v>54</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="E59" s="3">
         <v>9</v>
@@ -3029,61 +3207,58 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:6">
+    <row r="60" customHeight="1" spans="3:7">
       <c r="C60" s="3">
         <v>55</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="E60" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:6">
+    <row r="61" customHeight="1" spans="3:7">
       <c r="C61" s="3">
         <v>56</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="E61" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:6">
+    <row r="62" customHeight="1" spans="3:7">
       <c r="C62" s="3">
         <v>57</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="E62" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="3:6">
+    <row r="63" customHeight="1" spans="3:7">
       <c r="C63" s="3">
         <v>58</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E63" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="3:6">
+    <row r="64" customHeight="1" spans="3:7">
       <c r="C64" s="3">
         <v>59</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E64" s="3">
-        <v>10</v>
-      </c>
-      <c r="F64" s="3">
         <v>10</v>
       </c>
     </row>
@@ -3092,7 +3267,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E65" s="3">
         <v>10</v>
@@ -3106,7 +3281,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E66" s="3">
         <v>11</v>
@@ -3116,8 +3291,8 @@
       <c r="C67" s="3">
         <v>62</v>
       </c>
-      <c r="D67" s="15" t="s">
-        <v>164</v>
+      <c r="D67" s="16" t="s">
+        <v>183</v>
       </c>
       <c r="E67" s="3">
         <v>11</v>
@@ -3128,7 +3303,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E68" s="3">
         <v>11</v>
@@ -3139,7 +3314,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="E69" s="3">
         <v>11</v>
@@ -3150,12 +3325,9 @@
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="E70" s="3">
-        <v>11</v>
-      </c>
-      <c r="F70" s="3">
         <v>11</v>
       </c>
     </row>
@@ -3164,7 +3336,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E71" s="3">
         <v>11</v>
@@ -3178,7 +3350,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="E72" s="3">
         <v>12</v>
@@ -3189,7 +3361,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="E73" s="3">
         <v>12</v>
@@ -3200,7 +3372,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="E74" s="3">
         <v>12</v>
@@ -3211,7 +3383,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="E75" s="3">
         <v>12</v>
@@ -3222,12 +3394,9 @@
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="E76" s="3">
-        <v>12</v>
-      </c>
-      <c r="F76" s="3">
         <v>12</v>
       </c>
     </row>
@@ -3236,7 +3405,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="E77" s="3">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="192">
   <si>
     <t>_Id</t>
   </si>
@@ -114,25 +114,22 @@
     <t>暮色草场</t>
   </si>
   <si>
-    <t>2001,4001,5001</t>
-  </si>
-  <si>
-    <t>15,6000,6000</t>
+    <t>2001,4001,5001,3001</t>
+  </si>
+  <si>
+    <t>15,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180001</t>
   </si>
   <si>
-    <t>4000,8000</t>
+    <t>4000,6000</t>
   </si>
   <si>
     <t>磷火墓地</t>
   </si>
   <si>
-    <t>2002,4001,5001</t>
-  </si>
-  <si>
-    <t>16,6000,6000</t>
+    <t>2002,4001,5001,3001</t>
   </si>
   <si>
     <t>30001,180002</t>
@@ -141,10 +138,7 @@
     <t>碎骨荒原</t>
   </si>
   <si>
-    <t>2003,4001,5001</t>
-  </si>
-  <si>
-    <t>17,6000,6000</t>
+    <t>2003,4001,5001,3001</t>
   </si>
   <si>
     <t>30001,180003</t>
@@ -153,10 +147,7 @@
     <t>红月沙地</t>
   </si>
   <si>
-    <t>2004,4002,5001</t>
-  </si>
-  <si>
-    <t>18,6000,6000</t>
+    <t>2004,4002,5001,3001</t>
   </si>
   <si>
     <t>30001,180004</t>
@@ -165,10 +156,7 @@
     <t>黑石洞穴</t>
   </si>
   <si>
-    <t>2005,4002,5001</t>
-  </si>
-  <si>
-    <t>19,6000,6000</t>
+    <t>2005,4002,5001,3001</t>
   </si>
   <si>
     <t>30001,180005</t>
@@ -177,7 +165,7 @@
     <t>落日石阵</t>
   </si>
   <si>
-    <t>2006,4002,5001</t>
+    <t>2006,4002,5001,3001</t>
   </si>
   <si>
     <t>30001,180006</t>
@@ -186,10 +174,10 @@
     <t>腐卵泥潭</t>
   </si>
   <si>
-    <t>2007,4003,5002</t>
-  </si>
-  <si>
-    <t>20,6000,6000</t>
+    <t>2007,4003,5002,3001</t>
+  </si>
+  <si>
+    <t>16,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180007</t>
@@ -198,7 +186,7 @@
     <t>血色废墟</t>
   </si>
   <si>
-    <t>2008,4003,5002</t>
+    <t>2008,4003,5002,3001</t>
   </si>
   <si>
     <t>30001,180008</t>
@@ -207,7 +195,7 @@
     <t>裂土石径</t>
   </si>
   <si>
-    <t>2009,4003,5002</t>
+    <t>2009,4003,5002,3001</t>
   </si>
   <si>
     <t>30001,180009</t>
@@ -216,10 +204,7 @@
     <t>黑暗森林</t>
   </si>
   <si>
-    <t>2010,4004,5002</t>
-  </si>
-  <si>
-    <t>21,6000,6000</t>
+    <t>2010,4004,5002,3001</t>
   </si>
   <si>
     <t>30001,180010</t>
@@ -228,7 +213,7 @@
     <t>瘴气河湾</t>
   </si>
   <si>
-    <t>2011,4004,5002</t>
+    <t>2011,4004,5002,3001</t>
   </si>
   <si>
     <t>30001,180011</t>
@@ -237,7 +222,7 @@
     <t>剧毒泥潭</t>
   </si>
   <si>
-    <t>2012,4004,5002</t>
+    <t>2012,4004,5002,3001</t>
   </si>
   <si>
     <t>30001,180012</t>
@@ -246,10 +231,10 @@
     <t>废石小径</t>
   </si>
   <si>
-    <t>2013,4005,5003</t>
-  </si>
-  <si>
-    <t>22,6000,6000</t>
+    <t>2013,4005,5003,3002</t>
+  </si>
+  <si>
+    <t>17,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180013</t>
@@ -258,7 +243,7 @@
     <t>废弃矿道</t>
   </si>
   <si>
-    <t>2014,4005,5003</t>
+    <t>2014,4005,5003,3002</t>
   </si>
   <si>
     <t>30001,180014</t>
@@ -267,7 +252,7 @@
     <t>绝望坑道</t>
   </si>
   <si>
-    <t>2015,4005,5003</t>
+    <t>2015,4005,5003,3002</t>
   </si>
   <si>
     <t>30001,180015</t>
@@ -276,10 +261,7 @@
     <t>血煞溶洞</t>
   </si>
   <si>
-    <t>2016,4006,5003</t>
-  </si>
-  <si>
-    <t>23,6000,6000</t>
+    <t>2016,4006,5003,3002</t>
   </si>
   <si>
     <t>30001,180016</t>
@@ -288,7 +270,7 @@
     <t>归宿祭坛</t>
   </si>
   <si>
-    <t>2017,4006,5003</t>
+    <t>2017,4006,5003,3002</t>
   </si>
   <si>
     <t>30001,180017</t>
@@ -297,7 +279,7 @@
     <t>黄泉洞府</t>
   </si>
   <si>
-    <t>2018,4006,5003</t>
+    <t>2018,4006,5003,3002</t>
   </si>
   <si>
     <t>30001,180018</t>
@@ -306,10 +288,10 @@
     <t>魅惑花园</t>
   </si>
   <si>
-    <t>2019,4007,5004,3001</t>
-  </si>
-  <si>
-    <t>24,6000,6000,10000</t>
+    <t>2019,4007,5004,3002</t>
+  </si>
+  <si>
+    <t>18,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180019</t>
@@ -318,7 +300,7 @@
     <t>藤蔓密道</t>
   </si>
   <si>
-    <t>2020,4007,5004,3001</t>
+    <t>2020,4007,5004,3002</t>
   </si>
   <si>
     <t>30001,180020</t>
@@ -327,7 +309,7 @@
     <t>黑水潭</t>
   </si>
   <si>
-    <t>2021,4007,5004,3001</t>
+    <t>2021,4007,5004,3002</t>
   </si>
   <si>
     <t>30001,180021</t>
@@ -336,10 +318,7 @@
     <t>望月高台</t>
   </si>
   <si>
-    <t>2022,4007,5004,3001</t>
-  </si>
-  <si>
-    <t>25,6000,6000,10000</t>
+    <t>2022,4007,5004,3002</t>
   </si>
   <si>
     <t>30001,180022</t>
@@ -348,7 +327,7 @@
     <t>毒瘴山谷</t>
   </si>
   <si>
-    <t>2023,4007,5004,3001</t>
+    <t>2023,4007,5004,3002</t>
   </si>
   <si>
     <t>30001,180023</t>
@@ -357,7 +336,7 @@
     <t>梦境之树</t>
   </si>
   <si>
-    <t>2024,4007,5004,3001</t>
+    <t>2024,4007,5004,3002</t>
   </si>
   <si>
     <t>30001,180024</t>
@@ -366,10 +345,10 @@
     <t>荒漠边缘</t>
   </si>
   <si>
-    <t>2025,4007,5005,3002</t>
-  </si>
-  <si>
-    <t>26,6000,6000,10000</t>
+    <t>2025,4007,5005,3003</t>
+  </si>
+  <si>
+    <t>19,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180025</t>
@@ -378,7 +357,7 @@
     <t>遗忘高地</t>
   </si>
   <si>
-    <t>2026,4007,5005,3002</t>
+    <t>2026,4007,5005,3003</t>
   </si>
   <si>
     <t>30001,180026</t>
@@ -387,7 +366,7 @@
     <t>遗弃坟场</t>
   </si>
   <si>
-    <t>2027,4007,5005,3002</t>
+    <t>2027,4007,5005,3003</t>
   </si>
   <si>
     <t>30001,180027</t>
@@ -396,10 +375,7 @@
     <t>幽暗灵墓</t>
   </si>
   <si>
-    <t>2028,4007,5005,3002</t>
-  </si>
-  <si>
-    <t>27,6000,6000,10000</t>
+    <t>2028,4007,5005,3003</t>
   </si>
   <si>
     <t>30001,180028</t>
@@ -408,7 +384,7 @@
     <t>亡者塔楼</t>
   </si>
   <si>
-    <t>2029,4007,5005,3002</t>
+    <t>2029,4007,5005,3003</t>
   </si>
   <si>
     <t>30001,180029</t>
@@ -417,7 +393,7 @@
     <t>埋骨之地</t>
   </si>
   <si>
-    <t>2030,4007,5005,3002</t>
+    <t>2030,4007,5005,3003</t>
   </si>
   <si>
     <t>30001,180030</t>
@@ -429,7 +405,7 @@
     <t>2031,4007,5006,3003</t>
   </si>
   <si>
-    <t>28,6000,6000,10000</t>
+    <t>20,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180031</t>
@@ -459,9 +435,6 @@
     <t>2034,4007,5006,3003</t>
   </si>
   <si>
-    <t>29,6000,6000,10000</t>
-  </si>
-  <si>
     <t>30001,180034</t>
   </si>
   <si>
@@ -489,7 +462,7 @@
     <t>2037,4007,5007,3003</t>
   </si>
   <si>
-    <t>30,6000,6000,10000</t>
+    <t>21,5000,5000,8000</t>
   </si>
   <si>
     <t>30001,180037</t>
@@ -546,34 +519,55 @@
     <t>2043,4007,5008,3004</t>
   </si>
   <si>
+    <t>22,5000,5000,8000</t>
+  </si>
+  <si>
+    <t>30001,180043</t>
+  </si>
+  <si>
     <t>冰冷大厅</t>
   </si>
   <si>
     <t>2044,4007,5008,3004</t>
   </si>
   <si>
+    <t>30001,180044</t>
+  </si>
+  <si>
     <t>寒冰湖岸</t>
   </si>
   <si>
     <t>2045,4007,5008,3004</t>
   </si>
   <si>
+    <t>30001,180045</t>
+  </si>
+  <si>
     <t>冰霜平原</t>
   </si>
   <si>
     <t>2046,4007,5008,3004</t>
   </si>
   <si>
+    <t>30001,180046</t>
+  </si>
+  <si>
     <t>冰霜高地</t>
   </si>
   <si>
     <t>2047,4007,5008,3004</t>
   </si>
   <si>
+    <t>30001,180047</t>
+  </si>
+  <si>
     <t>凛冽王宫</t>
   </si>
   <si>
     <t>2048,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180048</t>
   </si>
   <si>
     <t>鬼眼蛛巢</t>
@@ -1331,10 +1325,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -1853,10 +1847,10 @@
         <v>21</v>
       </c>
       <c r="H7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="18" t="s">
         <v>22</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>23</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>19</v>
@@ -1873,19 +1867,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" s="3">
         <v>1</v>
       </c>
       <c r="G8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>25</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>27</v>
       </c>
       <c r="J8" s="17" t="s">
         <v>19</v>
@@ -1902,19 +1896,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
         <v>1</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I9" s="18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J9" s="17" t="s">
         <v>19</v>
@@ -1931,19 +1925,19 @@
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3">
         <v>1</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J10" s="17" t="s">
         <v>19</v>
@@ -1960,7 +1954,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1969,15 +1963,15 @@
         <v>1</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="3">
@@ -1992,19 +1986,19 @@
         <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3">
         <v>2</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I12" s="18" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J12" s="17" t="s">
         <v>19</v>
@@ -2021,19 +2015,19 @@
         <v>8</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E13" s="3">
         <v>2</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H13" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>45</v>
       </c>
       <c r="J13" s="17" t="s">
         <v>19</v>
@@ -2050,19 +2044,19 @@
         <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E14" s="3">
         <v>2</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J14" s="17" t="s">
         <v>19</v>
@@ -2079,19 +2073,19 @@
         <v>10</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E15" s="3">
         <v>2</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J15" s="17" t="s">
         <v>19</v>
@@ -2108,19 +2102,19 @@
         <v>11</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3">
         <v>2</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I16" s="18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J16" s="17" t="s">
         <v>19</v>
@@ -2137,7 +2131,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -2146,15 +2140,15 @@
         <v>2</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="J17" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="3">
@@ -2169,19 +2163,19 @@
         <v>13</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E18" s="3">
         <v>3</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J18" s="17" t="s">
         <v>19</v>
@@ -2198,19 +2192,19 @@
         <v>14</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E19" s="3">
         <v>3</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I19" s="18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J19" s="17" t="s">
         <v>19</v>
@@ -2227,19 +2221,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3">
         <v>3</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>19</v>
@@ -2256,19 +2250,19 @@
         <v>16</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E21" s="3">
         <v>3</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>19</v>
@@ -2285,19 +2279,19 @@
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3">
         <v>3</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>19</v>
@@ -2314,7 +2308,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -2323,15 +2317,15 @@
         <v>3</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="19" t="s">
         <v>71</v>
       </c>
+      <c r="H23" s="17" t="s">
+        <v>56</v>
+      </c>
       <c r="I23" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="J23" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="3">
@@ -2346,21 +2340,21 @@
         <v>19</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2">
         <v>4</v>
       </c>
       <c r="G24" s="21" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H24" s="21" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="J24" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K24" s="3">
@@ -2375,19 +2369,19 @@
         <v>20</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E25" s="3">
         <v>4</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>19</v>
@@ -2404,19 +2398,19 @@
         <v>21</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E26" s="3">
         <v>4</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="17" t="s">
         <v>81</v>
       </c>
+      <c r="H26" s="21" t="s">
+        <v>75</v>
+      </c>
       <c r="I26" s="18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>19</v>
@@ -2433,19 +2427,19 @@
         <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E27" s="3">
         <v>4</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>91</v>
+        <v>84</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>19</v>
@@ -2462,19 +2456,19 @@
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E28" s="3">
         <v>4</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>91</v>
+        <v>87</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="J28" s="17" t="s">
         <v>19</v>
@@ -2491,7 +2485,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E29" s="1">
         <v>4</v>
@@ -2500,15 +2494,15 @@
         <v>4</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="J29" s="19" t="s">
+      <c r="J29" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="3">
@@ -2523,21 +2517,21 @@
         <v>25</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H30" s="21" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="J30" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="3">
@@ -2552,19 +2546,19 @@
         <v>26</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E31" s="3">
         <v>5</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>101</v>
+        <v>97</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>19</v>
@@ -2581,19 +2575,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E32" s="3">
         <v>5</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="H32" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="18" t="s">
         <v>101</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>108</v>
       </c>
       <c r="J32" s="17" t="s">
         <v>19</v>
@@ -2610,19 +2604,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E33" s="3">
         <v>5</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>111</v>
+        <v>103</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="J33" s="17" t="s">
         <v>19</v>
@@ -2639,19 +2633,19 @@
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E34" s="3">
         <v>5</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="J34" s="17" t="s">
         <v>19</v>
@@ -2668,7 +2662,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E35" s="1">
         <v>5</v>
@@ -2677,15 +2671,15 @@
         <v>5</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="J35" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="3">
@@ -2700,19 +2694,19 @@
         <v>31</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E36" s="3">
         <v>6</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J36" s="17" t="s">
         <v>19</v>
@@ -2729,19 +2723,19 @@
         <v>32</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E37" s="3">
         <v>6</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J37" s="17" t="s">
         <v>19</v>
@@ -2758,19 +2752,19 @@
         <v>33</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E38" s="3">
         <v>6</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J38" s="17" t="s">
         <v>19</v>
@@ -2787,19 +2781,19 @@
         <v>34</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E39" s="3">
         <v>6</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J39" s="17" t="s">
         <v>19</v>
@@ -2816,19 +2810,19 @@
         <v>35</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E40" s="3">
         <v>6</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="J40" s="17" t="s">
         <v>19</v>
@@ -2845,7 +2839,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
@@ -2854,15 +2848,15 @@
         <v>6</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>113</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="J41" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="J41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="3">
@@ -2877,19 +2871,19 @@
         <v>37</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E42" s="3">
         <v>7</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>142</v>
+        <v>132</v>
+      </c>
+      <c r="I42" s="22" t="s">
+        <v>133</v>
       </c>
       <c r="J42" s="17" t="s">
         <v>19</v>
@@ -2906,19 +2900,19 @@
         <v>38</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E43" s="3">
         <v>7</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I43" s="23" t="s">
-        <v>145</v>
+        <v>132</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>136</v>
       </c>
       <c r="J43" s="17" t="s">
         <v>19</v>
@@ -2935,19 +2929,19 @@
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E44" s="3">
         <v>7</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I44" s="23" t="s">
-        <v>148</v>
+        <v>132</v>
+      </c>
+      <c r="I44" s="22" t="s">
+        <v>139</v>
       </c>
       <c r="J44" s="17" t="s">
         <v>19</v>
@@ -2964,19 +2958,19 @@
         <v>40</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E45" s="3">
         <v>7</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>151</v>
+        <v>132</v>
+      </c>
+      <c r="I45" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="J45" s="17" t="s">
         <v>19</v>
@@ -2992,21 +2986,21 @@
       <c r="C46" s="3">
         <v>41</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>152</v>
+      <c r="D46" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="E46" s="3">
         <v>7</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="17" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I46" s="23" t="s">
-        <v>154</v>
+        <v>132</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>145</v>
       </c>
       <c r="J46" s="17" t="s">
         <v>19</v>
@@ -3023,7 +3017,7 @@
         <v>42</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E47" s="3">
         <v>7</v>
@@ -3032,15 +3026,15 @@
         <v>7</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>141</v>
+        <v>147</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>132</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="J47" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="J47" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="3">
@@ -3055,78 +3049,152 @@
         <v>43</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E48" s="3">
         <v>8</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:7">
+        <v>150</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I48" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="3">
+        <v>60</v>
+      </c>
+      <c r="L48" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:12">
       <c r="C49" s="3">
         <v>44</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E49" s="3">
         <v>8</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:7">
+        <v>154</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I49" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="3">
+        <v>60</v>
+      </c>
+      <c r="L49" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:12">
       <c r="C50" s="3">
         <v>45</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E50" s="3">
         <v>8</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:7">
+        <v>157</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="3">
+        <v>60</v>
+      </c>
+      <c r="L50" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:12">
       <c r="C51" s="3">
         <v>46</v>
       </c>
-      <c r="D51" s="16" t="s">
-        <v>164</v>
+      <c r="D51" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="E51" s="3">
         <v>8</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:7">
+        <v>160</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="3">
+        <v>60</v>
+      </c>
+      <c r="L51" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:12">
       <c r="C52" s="3">
         <v>47</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E52" s="3">
         <v>8</v>
       </c>
-      <c r="F52" s="3"/>
       <c r="G52" s="17" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:7">
+        <v>163</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I52" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="3">
+        <v>60</v>
+      </c>
+      <c r="L52" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:12">
       <c r="C53" s="3">
         <v>48</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E53" s="3">
         <v>8</v>
@@ -3135,70 +3203,85 @@
         <v>8</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:7">
+        <v>166</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I53" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="J53" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="3">
+        <v>60</v>
+      </c>
+      <c r="L53" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:12">
       <c r="C54" s="3">
         <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E54" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="3:7">
+    <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="3">
         <v>50</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E55" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="3:7">
+    <row r="56" customHeight="1" spans="3:12">
       <c r="C56" s="3">
         <v>51</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E56" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="3:7">
+    <row r="57" customHeight="1" spans="3:12">
       <c r="C57" s="3">
         <v>52</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E57" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:7">
+    <row r="58" customHeight="1" spans="3:12">
       <c r="C58" s="3">
         <v>53</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E58" s="3">
         <v>9</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:7">
+    <row r="59" customHeight="1" spans="3:12">
       <c r="C59" s="3">
         <v>54</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E59" s="3">
         <v>9</v>
@@ -3207,56 +3290,56 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:7">
+    <row r="60" customHeight="1" spans="3:12">
       <c r="C60" s="3">
         <v>55</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E60" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="3:7">
+    <row r="61" customHeight="1" spans="3:12">
       <c r="C61" s="3">
         <v>56</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E61" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:7">
+    <row r="62" customHeight="1" spans="3:12">
       <c r="C62" s="3">
         <v>57</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E62" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="3:7">
+    <row r="63" customHeight="1" spans="3:12">
       <c r="C63" s="3">
         <v>58</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E63" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="3:7">
+    <row r="64" customHeight="1" spans="3:12">
       <c r="C64" s="3">
         <v>59</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E64" s="3">
         <v>10</v>
@@ -3267,7 +3350,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E65" s="3">
         <v>10</v>
@@ -3281,7 +3364,7 @@
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E66" s="3">
         <v>11</v>
@@ -3291,8 +3374,8 @@
       <c r="C67" s="3">
         <v>62</v>
       </c>
-      <c r="D67" s="16" t="s">
-        <v>183</v>
+      <c r="D67" s="15" t="s">
+        <v>181</v>
       </c>
       <c r="E67" s="3">
         <v>11</v>
@@ -3303,7 +3386,7 @@
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E68" s="3">
         <v>11</v>
@@ -3314,7 +3397,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E69" s="3">
         <v>11</v>
@@ -3325,7 +3408,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E70" s="3">
         <v>11</v>
@@ -3336,7 +3419,7 @@
         <v>66</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E71" s="3">
         <v>11</v>
@@ -3350,7 +3433,7 @@
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E72" s="3">
         <v>12</v>
@@ -3361,7 +3444,7 @@
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E73" s="3">
         <v>12</v>
@@ -3372,7 +3455,7 @@
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E74" s="3">
         <v>12</v>
@@ -3383,7 +3466,7 @@
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E75" s="3">
         <v>12</v>
@@ -3394,7 +3477,7 @@
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E76" s="3">
         <v>12</v>
@@ -3405,7 +3488,7 @@
         <v>72</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E77" s="3">
         <v>12</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="主线副本" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="244">
   <si>
     <t>_Id</t>
   </si>
@@ -573,73 +573,229 @@
     <t>鬼眼蛛巢</t>
   </si>
   <si>
+    <t>2049,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>23,5000,5000,8000</t>
+  </si>
+  <si>
+    <t>30001,180049</t>
+  </si>
+  <si>
     <t>毒云沼泽</t>
   </si>
   <si>
+    <t>2050,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180050</t>
+  </si>
+  <si>
     <t>剧毒湿地</t>
   </si>
   <si>
+    <t>2051,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180051</t>
+  </si>
+  <si>
     <t>午夜迷宫</t>
   </si>
   <si>
+    <t>2052,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180052</t>
+  </si>
+  <si>
     <t>祭祀高台</t>
   </si>
   <si>
+    <t>2053,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180053</t>
+  </si>
+  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
+    <t>2054,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180054</t>
+  </si>
+  <si>
     <t>半人马营地</t>
   </si>
   <si>
+    <t>2055,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>24,5000,5000,8000</t>
+  </si>
+  <si>
+    <t>30001,180055</t>
+  </si>
+  <si>
     <t>围猎场</t>
   </si>
   <si>
+    <t>2056,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180056</t>
+  </si>
+  <si>
     <t>萨满小屋</t>
   </si>
   <si>
+    <t>2057,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180057</t>
+  </si>
+  <si>
     <t>屠戮大厅</t>
   </si>
   <si>
+    <t>2058,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180058</t>
+  </si>
+  <si>
     <t>飞龙巢穴</t>
   </si>
   <si>
+    <t>2059,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180059</t>
+  </si>
+  <si>
     <t>王者角斗场</t>
   </si>
   <si>
+    <t>2060,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180060</t>
+  </si>
+  <si>
     <t>无尽裂隙</t>
   </si>
   <si>
+    <t>2061,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>25,5000,5000,8000</t>
+  </si>
+  <si>
+    <t>30001,180061</t>
+  </si>
+  <si>
     <t>寂灭之地</t>
   </si>
   <si>
+    <t>2062,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180062</t>
+  </si>
+  <si>
     <t>猩红之界</t>
   </si>
   <si>
+    <t>2063,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180063</t>
+  </si>
+  <si>
     <t>起源之地</t>
   </si>
   <si>
+    <t>2064,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180064</t>
+  </si>
+  <si>
     <t>虚无战场</t>
   </si>
   <si>
+    <t>2065,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180065</t>
+  </si>
+  <si>
     <t>神王宝座</t>
   </si>
   <si>
+    <t>2066,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180066</t>
+  </si>
+  <si>
     <t>熔炉外围</t>
   </si>
   <si>
+    <t>2067,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>26,5000,5000,8000</t>
+  </si>
+  <si>
+    <t>30001,180067</t>
+  </si>
+  <si>
     <t>地狱之门</t>
   </si>
   <si>
+    <t>2068,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180068</t>
+  </si>
+  <si>
     <t>女巫宫殿</t>
   </si>
   <si>
+    <t>2069,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180069</t>
+  </si>
+  <si>
     <t>地狱猎场</t>
   </si>
   <si>
+    <t>2070,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180070</t>
+  </si>
+  <si>
     <t>烈焰祭坛</t>
   </si>
   <si>
+    <t>2071,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180071</t>
+  </si>
+  <si>
     <t>毁灭王座</t>
+  </si>
+  <si>
+    <t>2072,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180072</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +1451,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1328,13 +1484,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1814,16 +1968,16 @@
       <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="17" t="s">
+      <c r="J6" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="3">
@@ -1843,16 +1997,16 @@
       <c r="E7" s="3">
         <v>1</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="3">
@@ -1872,16 +2026,16 @@
       <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="3">
@@ -1901,16 +2055,16 @@
       <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="17" t="s">
+      <c r="J9" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="3">
@@ -1930,16 +2084,16 @@
       <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="3">
@@ -1962,16 +2116,16 @@
       <c r="F11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="3">
@@ -1991,16 +2145,16 @@
       <c r="E12" s="3">
         <v>2</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="3">
@@ -2020,16 +2174,16 @@
       <c r="E13" s="3">
         <v>2</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="3">
@@ -2049,16 +2203,16 @@
       <c r="E14" s="3">
         <v>2</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="3">
@@ -2078,16 +2232,16 @@
       <c r="E15" s="3">
         <v>2</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="G15" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="3">
@@ -2107,16 +2261,16 @@
       <c r="E16" s="3">
         <v>2</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="3">
@@ -2139,16 +2293,16 @@
       <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="3">
@@ -2168,16 +2322,16 @@
       <c r="E18" s="3">
         <v>3</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="18" t="s">
+      <c r="I18" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="17" t="s">
+      <c r="J18" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="3">
@@ -2197,16 +2351,16 @@
       <c r="E19" s="3">
         <v>3</v>
       </c>
-      <c r="G19" s="17" t="s">
+      <c r="G19" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="17" t="s">
+      <c r="J19" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="3">
@@ -2226,16 +2380,16 @@
       <c r="E20" s="3">
         <v>3</v>
       </c>
-      <c r="G20" s="17" t="s">
+      <c r="G20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="J20" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="3">
@@ -2255,16 +2409,16 @@
       <c r="E21" s="3">
         <v>3</v>
       </c>
-      <c r="G21" s="17" t="s">
+      <c r="G21" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="J21" s="17" t="s">
+      <c r="J21" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="3">
@@ -2284,16 +2438,16 @@
       <c r="E22" s="3">
         <v>3</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="3">
@@ -2316,16 +2470,16 @@
       <c r="F23" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J23" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="3">
@@ -2345,16 +2499,16 @@
       <c r="E24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="G24" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K24" s="3">
@@ -2374,16 +2528,16 @@
       <c r="E25" s="3">
         <v>4</v>
       </c>
-      <c r="G25" s="17" t="s">
+      <c r="G25" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H25" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="I25" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="3">
@@ -2403,16 +2557,16 @@
       <c r="E26" s="3">
         <v>4</v>
       </c>
-      <c r="G26" s="17" t="s">
+      <c r="G26" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="18" t="s">
+      <c r="I26" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="J26" s="17" t="s">
+      <c r="J26" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="3">
@@ -2432,16 +2586,16 @@
       <c r="E27" s="3">
         <v>4</v>
       </c>
-      <c r="G27" s="17" t="s">
+      <c r="G27" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="J27" s="17" t="s">
+      <c r="J27" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="3">
@@ -2461,16 +2615,16 @@
       <c r="E28" s="3">
         <v>4</v>
       </c>
-      <c r="G28" s="17" t="s">
+      <c r="G28" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="21" t="s">
+      <c r="H28" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="17" t="s">
+      <c r="J28" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="3">
@@ -2493,16 +2647,16 @@
       <c r="F29" s="1">
         <v>4</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="I29" s="20" t="s">
+      <c r="I29" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="J29" s="17" t="s">
+      <c r="J29" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="3">
@@ -2522,16 +2676,16 @@
       <c r="E30" s="2">
         <v>5</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G30" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H30" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="J30" s="17" t="s">
+      <c r="J30" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="3">
@@ -2551,16 +2705,16 @@
       <c r="E31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="H31" s="21" t="s">
+      <c r="H31" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I31" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J31" s="17" t="s">
+      <c r="J31" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K31" s="3">
@@ -2580,16 +2734,16 @@
       <c r="E32" s="3">
         <v>5</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I32" s="18" t="s">
+      <c r="I32" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="J32" s="17" t="s">
+      <c r="J32" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K32" s="3">
@@ -2609,16 +2763,16 @@
       <c r="E33" s="3">
         <v>5</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="21" t="s">
+      <c r="H33" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I33" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="J33" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="3">
@@ -2638,16 +2792,16 @@
       <c r="E34" s="3">
         <v>5</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I34" s="18" t="s">
+      <c r="I34" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="J34" s="17" t="s">
+      <c r="J34" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="3">
@@ -2670,16 +2824,16 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H35" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="I35" s="20" t="s">
+      <c r="I35" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="17" t="s">
+      <c r="J35" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="3">
@@ -2699,16 +2853,16 @@
       <c r="E36" s="3">
         <v>6</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I36" s="18" t="s">
+      <c r="I36" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="J36" s="17" t="s">
+      <c r="J36" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="3">
@@ -2728,16 +2882,16 @@
       <c r="E37" s="3">
         <v>6</v>
       </c>
-      <c r="G37" s="17" t="s">
+      <c r="G37" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="18" t="s">
+      <c r="I37" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="J37" s="17" t="s">
+      <c r="J37" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="3">
@@ -2757,16 +2911,16 @@
       <c r="E38" s="3">
         <v>6</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G38" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H38" s="17" t="s">
+      <c r="H38" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="18" t="s">
+      <c r="I38" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="J38" s="17" t="s">
+      <c r="J38" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="3">
@@ -2786,16 +2940,16 @@
       <c r="E39" s="3">
         <v>6</v>
       </c>
-      <c r="G39" s="17" t="s">
+      <c r="G39" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I39" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="J39" s="17" t="s">
+      <c r="J39" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="3">
@@ -2815,16 +2969,16 @@
       <c r="E40" s="3">
         <v>6</v>
       </c>
-      <c r="G40" s="17" t="s">
+      <c r="G40" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="H40" s="17" t="s">
+      <c r="H40" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I40" s="18" t="s">
+      <c r="I40" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="J40" s="17" t="s">
+      <c r="J40" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="3">
@@ -2847,16 +3001,16 @@
       <c r="F41" s="1">
         <v>6</v>
       </c>
-      <c r="G41" s="19" t="s">
+      <c r="G41" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="J41" s="17" t="s">
+      <c r="J41" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="3">
@@ -2876,16 +3030,16 @@
       <c r="E42" s="3">
         <v>7</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="G42" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="H42" s="17" t="s">
+      <c r="H42" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I42" s="22" t="s">
+      <c r="I42" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="J42" s="17" t="s">
+      <c r="J42" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="3">
@@ -2905,16 +3059,16 @@
       <c r="E43" s="3">
         <v>7</v>
       </c>
-      <c r="G43" s="17" t="s">
+      <c r="G43" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="H43" s="17" t="s">
+      <c r="H43" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I43" s="22" t="s">
+      <c r="I43" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="J43" s="17" t="s">
+      <c r="J43" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K43" s="3">
@@ -2934,16 +3088,16 @@
       <c r="E44" s="3">
         <v>7</v>
       </c>
-      <c r="G44" s="17" t="s">
+      <c r="G44" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="H44" s="17" t="s">
+      <c r="H44" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I44" s="22" t="s">
+      <c r="I44" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="J44" s="17" t="s">
+      <c r="J44" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K44" s="3">
@@ -2963,16 +3117,16 @@
       <c r="E45" s="3">
         <v>7</v>
       </c>
-      <c r="G45" s="17" t="s">
+      <c r="G45" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="H45" s="17" t="s">
+      <c r="H45" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I45" s="22" t="s">
+      <c r="I45" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="J45" s="17" t="s">
+      <c r="J45" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="3">
@@ -2993,16 +3147,16 @@
         <v>7</v>
       </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="17" t="s">
+      <c r="G46" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="H46" s="17" t="s">
+      <c r="H46" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I46" s="22" t="s">
+      <c r="I46" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="J46" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="3">
@@ -3025,16 +3179,16 @@
       <c r="F47" s="3">
         <v>7</v>
       </c>
-      <c r="G47" s="19" t="s">
+      <c r="G47" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="H47" s="17" t="s">
+      <c r="H47" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="20" t="s">
+      <c r="I47" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="J47" s="17" t="s">
+      <c r="J47" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="3">
@@ -3054,16 +3208,16 @@
       <c r="E48" s="3">
         <v>8</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G48" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="H48" s="17" t="s">
+      <c r="H48" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="23" t="s">
+      <c r="I48" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="J48" s="17" t="s">
+      <c r="J48" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="3">
@@ -3083,16 +3237,16 @@
       <c r="E49" s="3">
         <v>8</v>
       </c>
-      <c r="G49" s="17" t="s">
+      <c r="G49" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="H49" s="17" t="s">
+      <c r="H49" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I49" s="23" t="s">
+      <c r="I49" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="J49" s="17" t="s">
+      <c r="J49" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="3">
@@ -3112,16 +3266,16 @@
       <c r="E50" s="3">
         <v>8</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="H50" s="17" t="s">
+      <c r="H50" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I50" s="23" t="s">
+      <c r="I50" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="J50" s="17" t="s">
+      <c r="J50" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="3">
@@ -3141,16 +3295,16 @@
       <c r="E51" s="3">
         <v>8</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="H51" s="17" t="s">
+      <c r="H51" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I51" s="23" t="s">
+      <c r="I51" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="J51" s="17" t="s">
+      <c r="J51" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="3">
@@ -3170,16 +3324,16 @@
       <c r="E52" s="3">
         <v>8</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="G52" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="17" t="s">
+      <c r="H52" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I52" s="23" t="s">
+      <c r="I52" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="J52" s="17" t="s">
+      <c r="J52" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="3">
@@ -3202,16 +3356,16 @@
       <c r="F53" s="3">
         <v>8</v>
       </c>
-      <c r="G53" s="17" t="s">
+      <c r="G53" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I53" s="20" t="s">
+      <c r="I53" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="J53" s="17" t="s">
+      <c r="J53" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="3">
@@ -3231,16 +3385,40 @@
       <c r="E54" s="3">
         <v>9</v>
       </c>
+      <c r="G54" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="3">
         <v>50</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E55" s="3">
         <v>9</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:12">
@@ -3248,10 +3426,22 @@
         <v>51</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E56" s="3">
         <v>9</v>
+      </c>
+      <c r="G56" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I56" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:12">
@@ -3259,10 +3449,22 @@
         <v>52</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E57" s="3">
         <v>9</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I57" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="J57" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:12">
@@ -3270,10 +3472,22 @@
         <v>53</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E58" s="3">
         <v>9</v>
+      </c>
+      <c r="G58" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:12">
@@ -3281,13 +3495,25 @@
         <v>54</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E59" s="3">
         <v>9</v>
       </c>
       <c r="F59" s="3">
         <v>9</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:12">
@@ -3295,10 +3521,22 @@
         <v>55</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="E60" s="3">
         <v>10</v>
+      </c>
+      <c r="G60" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="J60" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:12">
@@ -3306,10 +3544,22 @@
         <v>56</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E61" s="3">
         <v>10</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="J61" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:12">
@@ -3317,10 +3567,22 @@
         <v>57</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E62" s="3">
         <v>10</v>
+      </c>
+      <c r="G62" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="J62" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:12">
@@ -3328,10 +3590,22 @@
         <v>58</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="E63" s="3">
         <v>10</v>
+      </c>
+      <c r="G63" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:12">
@@ -3339,18 +3613,30 @@
         <v>59</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E64" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:6">
+      <c r="G64" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="J64" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
       <c r="C65" s="3">
         <v>60</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="E65" s="3">
         <v>10</v>
@@ -3358,68 +3644,140 @@
       <c r="F65" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:6">
+      <c r="G65" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="J65" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
       <c r="C66" s="3">
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E66" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:6">
+      <c r="G66" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I66" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="J66" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
       <c r="C67" s="3">
         <v>62</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="E67" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:6">
+      <c r="G67" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I67" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
       <c r="C68" s="3">
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="E68" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:6">
+      <c r="G68" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I68" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
       <c r="C69" s="3">
         <v>64</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="E69" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:6">
+      <c r="G69" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I69" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
       <c r="C70" s="3">
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="E70" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:6">
+      <c r="G70" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I70" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
       <c r="C71" s="3">
         <v>66</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="E71" s="3">
         <v>11</v>
@@ -3427,74 +3785,158 @@
       <c r="F71" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:6">
+      <c r="G71" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I71" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
       <c r="C72" s="3">
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="E72" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:6">
+      <c r="G72" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I72" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
       <c r="C73" s="3">
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="E73" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:6">
+      <c r="G73" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I73" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="J73" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
       <c r="C74" s="3">
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="E74" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:6">
+      <c r="G74" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I74" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
       <c r="C75" s="3">
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="E75" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:6">
+      <c r="G75" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
       <c r="C76" s="3">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="E76" s="3">
         <v>12</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:6">
+      <c r="G76" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="J76" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
       <c r="C77" s="3">
         <v>72</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="E77" s="3">
         <v>12</v>
       </c>
       <c r="F77" s="3">
         <v>12</v>
+      </c>
+      <c r="G77" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I77" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="J77" s="16" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="主线副本" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="245">
   <si>
     <t>_Id</t>
   </si>
@@ -682,6 +682,9 @@
   </si>
   <si>
     <t>30001,180060</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>无尽裂隙</t>
@@ -1847,7 +1850,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L77"/>
+  <dimension ref="A3:L77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="3" customWidth="1"/>
@@ -3631,7 +3634,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:10">
+    <row r="65" customHeight="1" spans="1:10">
       <c r="C65" s="3">
         <v>60</v>
       </c>
@@ -3657,127 +3660,163 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:10">
+    <row r="66" customHeight="1" spans="1:10">
+      <c r="A66" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C66" s="3">
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E66" s="3">
         <v>11</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J66" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:10">
+    <row r="67" customHeight="1" spans="1:10">
+      <c r="A67" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C67" s="3">
         <v>62</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E67" s="3">
         <v>11</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J67" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="3:10">
+    <row r="68" customHeight="1" spans="1:10">
+      <c r="A68" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C68" s="3">
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E68" s="3">
         <v>11</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J68" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:10">
+    <row r="69" customHeight="1" spans="1:10">
+      <c r="A69" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C69" s="3">
         <v>64</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E69" s="3">
         <v>11</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J69" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="3:10">
+    <row r="70" customHeight="1" spans="1:10">
+      <c r="A70" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C70" s="3">
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E70" s="3">
         <v>11</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J70" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="3:10">
+    <row r="71" customHeight="1" spans="1:10">
+      <c r="A71" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C71" s="3">
         <v>66</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E71" s="3">
         <v>11</v>
@@ -3786,139 +3825,175 @@
         <v>11</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J71" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="3:10">
+    <row r="72" customHeight="1" spans="1:10">
+      <c r="A72" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C72" s="3">
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E72" s="3">
         <v>12</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J72" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="3:10">
+    <row r="73" customHeight="1" spans="1:10">
+      <c r="A73" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C73" s="3">
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E73" s="3">
         <v>12</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J73" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="3:10">
+    <row r="74" customHeight="1" spans="1:10">
+      <c r="A74" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C74" s="3">
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E74" s="3">
         <v>12</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J74" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:10">
+    <row r="75" customHeight="1" spans="1:10">
+      <c r="A75" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C75" s="3">
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E75" s="3">
         <v>12</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I75" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J75" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:10">
+    <row r="76" customHeight="1" spans="1:10">
+      <c r="A76" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C76" s="3">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E76" s="3">
         <v>12</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J76" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:10">
+    <row r="77" customHeight="1" spans="1:10">
+      <c r="A77" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C77" s="3">
         <v>72</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E77" s="3">
         <v>12</v>
@@ -3927,13 +4002,13 @@
         <v>12</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J77" s="16" t="s">
         <v>19</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="主线副本" sheetId="1" r:id="rId1"/>
@@ -573,7 +573,7 @@
     <t>鬼眼蛛巢</t>
   </si>
   <si>
-    <t>2049,4007,5008,3004</t>
+    <t>2049,4007,5009,3004</t>
   </si>
   <si>
     <t>23,5000,5000,8000</t>
@@ -585,7 +585,7 @@
     <t>毒云沼泽</t>
   </si>
   <si>
-    <t>2050,4007,5008,3004</t>
+    <t>2050,4007,5009,3004</t>
   </si>
   <si>
     <t>30001,180050</t>
@@ -594,7 +594,7 @@
     <t>剧毒湿地</t>
   </si>
   <si>
-    <t>2051,4007,5008,3004</t>
+    <t>2051,4007,5009,3004</t>
   </si>
   <si>
     <t>30001,180051</t>
@@ -603,7 +603,7 @@
     <t>午夜迷宫</t>
   </si>
   <si>
-    <t>2052,4007,5008,3004</t>
+    <t>2052,4007,5009,3004</t>
   </si>
   <si>
     <t>30001,180052</t>
@@ -612,7 +612,7 @@
     <t>祭祀高台</t>
   </si>
   <si>
-    <t>2053,4007,5008,3004</t>
+    <t>2053,4007,5009,3004</t>
   </si>
   <si>
     <t>30001,180053</t>
@@ -621,7 +621,7 @@
     <t>诅咒祭坛</t>
   </si>
   <si>
-    <t>2054,4007,5008,3004</t>
+    <t>2054,4007,5009,3004</t>
   </si>
   <si>
     <t>30001,180054</t>
@@ -630,7 +630,7 @@
     <t>半人马营地</t>
   </si>
   <si>
-    <t>2055,4007,5008,3004</t>
+    <t>2055,4007,5010,3004</t>
   </si>
   <si>
     <t>24,5000,5000,8000</t>
@@ -642,7 +642,7 @@
     <t>围猎场</t>
   </si>
   <si>
-    <t>2056,4007,5008,3004</t>
+    <t>2056,4007,5010,3004</t>
   </si>
   <si>
     <t>30001,180056</t>
@@ -651,7 +651,7 @@
     <t>萨满小屋</t>
   </si>
   <si>
-    <t>2057,4007,5008,3004</t>
+    <t>2057,4007,5010,3004</t>
   </si>
   <si>
     <t>30001,180057</t>
@@ -660,7 +660,7 @@
     <t>屠戮大厅</t>
   </si>
   <si>
-    <t>2058,4007,5008,3004</t>
+    <t>2058,4007,5010,3004</t>
   </si>
   <si>
     <t>30001,180058</t>
@@ -669,7 +669,7 @@
     <t>飞龙巢穴</t>
   </si>
   <si>
-    <t>2059,4007,5008,3004</t>
+    <t>2059,4007,5010,3004</t>
   </si>
   <si>
     <t>30001,180059</t>
@@ -678,7 +678,7 @@
     <t>王者角斗场</t>
   </si>
   <si>
-    <t>2060,4007,5008,3004</t>
+    <t>2060,4007,5010,3004</t>
   </si>
   <si>
     <t>30001,180060</t>
@@ -690,7 +690,7 @@
     <t>无尽裂隙</t>
   </si>
   <si>
-    <t>2061,4007,5008,3004</t>
+    <t>2061,4007,5011,3004</t>
   </si>
   <si>
     <t>25,5000,5000,8000</t>
@@ -702,7 +702,7 @@
     <t>寂灭之地</t>
   </si>
   <si>
-    <t>2062,4007,5008,3004</t>
+    <t>2062,4007,5011,3004</t>
   </si>
   <si>
     <t>30001,180062</t>
@@ -711,7 +711,7 @@
     <t>猩红之界</t>
   </si>
   <si>
-    <t>2063,4007,5008,3004</t>
+    <t>2063,4007,5011,3004</t>
   </si>
   <si>
     <t>30001,180063</t>
@@ -720,7 +720,7 @@
     <t>起源之地</t>
   </si>
   <si>
-    <t>2064,4007,5008,3004</t>
+    <t>2064,4007,5011,3004</t>
   </si>
   <si>
     <t>30001,180064</t>
@@ -729,7 +729,7 @@
     <t>虚无战场</t>
   </si>
   <si>
-    <t>2065,4007,5008,3004</t>
+    <t>2065,4007,5011,3004</t>
   </si>
   <si>
     <t>30001,180065</t>
@@ -738,7 +738,7 @@
     <t>神王宝座</t>
   </si>
   <si>
-    <t>2066,4007,5008,3004</t>
+    <t>2066,4007,5011,3004</t>
   </si>
   <si>
     <t>30001,180066</t>
@@ -747,7 +747,7 @@
     <t>熔炉外围</t>
   </si>
   <si>
-    <t>2067,4007,5008,3004</t>
+    <t>2067,4007,5012,3004</t>
   </si>
   <si>
     <t>26,5000,5000,8000</t>
@@ -759,7 +759,7 @@
     <t>地狱之门</t>
   </si>
   <si>
-    <t>2068,4007,5008,3004</t>
+    <t>2068,4007,5012,3004</t>
   </si>
   <si>
     <t>30001,180068</t>
@@ -768,7 +768,7 @@
     <t>女巫宫殿</t>
   </si>
   <si>
-    <t>2069,4007,5008,3004</t>
+    <t>2069,4007,5012,3004</t>
   </si>
   <si>
     <t>30001,180069</t>
@@ -777,7 +777,7 @@
     <t>地狱猎场</t>
   </si>
   <si>
-    <t>2070,4007,5008,3004</t>
+    <t>2070,4007,5012,3004</t>
   </si>
   <si>
     <t>30001,180070</t>
@@ -786,7 +786,7 @@
     <t>烈焰祭坛</t>
   </si>
   <si>
-    <t>2071,4007,5008,3004</t>
+    <t>2071,4007,5012,3004</t>
   </si>
   <si>
     <t>30001,180071</t>
@@ -795,7 +795,7 @@
     <t>毁灭王座</t>
   </si>
   <si>
-    <t>2072,4007,5008,3004</t>
+    <t>2072,4007,5012,3004</t>
   </si>
   <si>
     <t>30001,180072</t>
@@ -3169,35 +3169,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:12">
-      <c r="C47" s="3">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C47" s="1">
         <v>42</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="1">
         <v>7</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="1">
         <v>7</v>
       </c>
       <c r="G47" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="H47" s="18" t="s">
         <v>132</v>
       </c>
       <c r="I47" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="J47" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="J47" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="1">
         <v>60</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="1">
         <v>60</v>
       </c>
     </row>
@@ -3346,35 +3346,35 @@
         <v>60</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="3:12">
-      <c r="C53" s="3">
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C53" s="1">
         <v>48</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="3">
+      <c r="E53" s="1">
         <v>8</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="1">
         <v>8</v>
       </c>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="18" t="s">
         <v>151</v>
       </c>
       <c r="I53" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="J53" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K53" s="3">
+      <c r="J53" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="1">
         <v>60</v>
       </c>
-      <c r="L53" s="3">
+      <c r="L53" s="1">
         <v>60</v>
       </c>
     </row>
@@ -3493,29 +3493,29 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:12">
-      <c r="C59" s="3">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C59" s="1">
         <v>54</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="1">
         <v>9</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="1">
         <v>9</v>
       </c>
-      <c r="G59" s="17" t="s">
+      <c r="G59" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="18" t="s">
         <v>170</v>
       </c>
       <c r="I59" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="J59" s="16" t="s">
+      <c r="J59" s="18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3634,29 +3634,29 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:10">
-      <c r="C65" s="3">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="C65" s="1">
         <v>60</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="D65" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E65" s="1">
         <v>10</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65" s="1">
         <v>10</v>
       </c>
-      <c r="G65" s="17" t="s">
+      <c r="G65" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="18" t="s">
         <v>189</v>
       </c>
       <c r="I65" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="J65" s="16" t="s">
+      <c r="J65" s="18" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3805,35 +3805,35 @@
         <v>19</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:10">
-      <c r="A71" s="3" t="s">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A71" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="1">
         <v>66</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E71" s="1">
         <v>11</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71" s="1">
         <v>11</v>
       </c>
-      <c r="G71" s="17" t="s">
+      <c r="G71" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="H71" s="16" t="s">
+      <c r="H71" s="18" t="s">
         <v>209</v>
       </c>
       <c r="I71" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="J71" s="16" t="s">
+      <c r="J71" s="18" t="s">
         <v>19</v>
       </c>
     </row>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="244">
   <si>
     <t>_Id</t>
   </si>
@@ -682,9 +682,6 @@
   </si>
   <si>
     <t>30001,180060</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
   <si>
     <t>无尽裂隙</t>
@@ -1850,7 +1847,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L77"/>
+  <dimension ref="C3:L77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="3" customWidth="1"/>
@@ -3400,6 +3397,12 @@
       <c r="J54" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K54" s="3">
+        <v>60</v>
+      </c>
+      <c r="L54" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="3">
@@ -3423,6 +3426,12 @@
       <c r="J55" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K55" s="3">
+        <v>60</v>
+      </c>
+      <c r="L55" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="56" customHeight="1" spans="3:12">
       <c r="C56" s="3">
@@ -3446,6 +3455,12 @@
       <c r="J56" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K56" s="3">
+        <v>60</v>
+      </c>
+      <c r="L56" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="57" customHeight="1" spans="3:12">
       <c r="C57" s="3">
@@ -3469,6 +3484,12 @@
       <c r="J57" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K57" s="3">
+        <v>60</v>
+      </c>
+      <c r="L57" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="58" customHeight="1" spans="3:12">
       <c r="C58" s="3">
@@ -3492,6 +3513,12 @@
       <c r="J58" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K58" s="3">
+        <v>60</v>
+      </c>
+      <c r="L58" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C59" s="1">
@@ -3518,6 +3545,12 @@
       <c r="J59" s="18" t="s">
         <v>19</v>
       </c>
+      <c r="K59" s="1">
+        <v>60</v>
+      </c>
+      <c r="L59" s="1">
+        <v>60</v>
+      </c>
     </row>
     <row r="60" customHeight="1" spans="3:12">
       <c r="C60" s="3">
@@ -3541,6 +3574,12 @@
       <c r="J60" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K60" s="3">
+        <v>60</v>
+      </c>
+      <c r="L60" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="61" customHeight="1" spans="3:12">
       <c r="C61" s="3">
@@ -3564,6 +3603,12 @@
       <c r="J61" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K61" s="3">
+        <v>60</v>
+      </c>
+      <c r="L61" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="62" customHeight="1" spans="3:12">
       <c r="C62" s="3">
@@ -3587,6 +3632,12 @@
       <c r="J62" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K62" s="3">
+        <v>60</v>
+      </c>
+      <c r="L62" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="63" customHeight="1" spans="3:12">
       <c r="C63" s="3">
@@ -3610,6 +3661,12 @@
       <c r="J63" s="16" t="s">
         <v>19</v>
       </c>
+      <c r="K63" s="3">
+        <v>60</v>
+      </c>
+      <c r="L63" s="3">
+        <v>60</v>
+      </c>
     </row>
     <row r="64" customHeight="1" spans="3:12">
       <c r="C64" s="3">
@@ -3633,8 +3690,14 @@
       <c r="J64" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="K64" s="3">
+        <v>60</v>
+      </c>
+      <c r="L64" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C65" s="1">
         <v>60</v>
       </c>
@@ -3659,164 +3722,164 @@
       <c r="J65" s="18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:10">
-      <c r="A66" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K65" s="1">
+        <v>60</v>
+      </c>
+      <c r="L65" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:12">
       <c r="C66" s="3">
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E66" s="3">
         <v>11</v>
       </c>
       <c r="G66" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="I66" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="I66" s="19" t="s">
-        <v>210</v>
-      </c>
       <c r="J66" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:10">
-      <c r="A67" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K66" s="3">
+        <v>60</v>
+      </c>
+      <c r="L66" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:12">
       <c r="C67" s="3">
         <v>62</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E67" s="3">
         <v>11</v>
       </c>
       <c r="G67" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I67" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H67" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I67" s="19" t="s">
-        <v>213</v>
-      </c>
       <c r="J67" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:10">
-      <c r="A68" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K67" s="3">
+        <v>60</v>
+      </c>
+      <c r="L67" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:12">
       <c r="C68" s="3">
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E68" s="3">
         <v>11</v>
       </c>
       <c r="G68" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I68" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="H68" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I68" s="19" t="s">
-        <v>216</v>
-      </c>
       <c r="J68" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:10">
-      <c r="A69" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K68" s="3">
+        <v>60</v>
+      </c>
+      <c r="L68" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:12">
       <c r="C69" s="3">
         <v>64</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E69" s="3">
         <v>11</v>
       </c>
       <c r="G69" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I69" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="H69" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I69" s="19" t="s">
-        <v>219</v>
-      </c>
       <c r="J69" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:10">
-      <c r="A70" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K69" s="3">
+        <v>60</v>
+      </c>
+      <c r="L69" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:12">
       <c r="C70" s="3">
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E70" s="3">
         <v>11</v>
       </c>
       <c r="G70" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="I70" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="H70" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="I70" s="19" t="s">
-        <v>222</v>
-      </c>
       <c r="J70" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A71" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>206</v>
-      </c>
+      <c r="K70" s="3">
+        <v>60</v>
+      </c>
+      <c r="L70" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C71" s="1">
         <v>66</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E71" s="1">
         <v>11</v>
@@ -3825,175 +3888,175 @@
         <v>11</v>
       </c>
       <c r="G71" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="I71" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="H71" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="I71" s="19" t="s">
-        <v>225</v>
-      </c>
       <c r="J71" s="18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:10">
-      <c r="A72" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K71" s="1">
+        <v>60</v>
+      </c>
+      <c r="L71" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:12">
       <c r="C72" s="3">
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E72" s="3">
         <v>12</v>
       </c>
       <c r="G72" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="H72" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="I72" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="I72" s="19" t="s">
-        <v>229</v>
-      </c>
       <c r="J72" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:10">
-      <c r="A73" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K72" s="3">
+        <v>60</v>
+      </c>
+      <c r="L72" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:12">
       <c r="C73" s="3">
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E73" s="3">
         <v>12</v>
       </c>
       <c r="G73" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I73" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="H73" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I73" s="19" t="s">
-        <v>232</v>
-      </c>
       <c r="J73" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:10">
-      <c r="A74" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K73" s="3">
+        <v>60</v>
+      </c>
+      <c r="L73" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:12">
       <c r="C74" s="3">
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E74" s="3">
         <v>12</v>
       </c>
       <c r="G74" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I74" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="H74" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I74" s="19" t="s">
-        <v>235</v>
-      </c>
       <c r="J74" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="1:10">
-      <c r="A75" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K74" s="3">
+        <v>60</v>
+      </c>
+      <c r="L74" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="3">
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E75" s="3">
         <v>12</v>
       </c>
       <c r="G75" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I75" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="H75" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I75" s="19" t="s">
-        <v>238</v>
-      </c>
       <c r="J75" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:10">
-      <c r="A76" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K75" s="3">
+        <v>60</v>
+      </c>
+      <c r="L75" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="3">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E76" s="3">
         <v>12</v>
       </c>
       <c r="G76" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I76" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H76" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I76" s="19" t="s">
-        <v>241</v>
-      </c>
       <c r="J76" s="16" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="1:10">
-      <c r="A77" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="K76" s="3">
+        <v>60</v>
+      </c>
+      <c r="L76" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="3">
         <v>72</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E77" s="3">
         <v>12</v>
@@ -4002,16 +4065,22 @@
         <v>12</v>
       </c>
       <c r="G77" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="I77" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="H77" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="I77" s="19" t="s">
-        <v>244</v>
-      </c>
       <c r="J77" s="16" t="s">
         <v>19</v>
+      </c>
+      <c r="K77" s="1">
+        <v>60</v>
+      </c>
+      <c r="L77" s="1">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
